--- a/data/nzd0075/nzd0075.xlsx
+++ b/data/nzd0075/nzd0075.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U351"/>
+  <dimension ref="A1:U352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24681,6 +24681,75 @@
         <v>362.93</v>
       </c>
       <c r="U351" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>370.97</v>
+      </c>
+      <c r="C352" t="n">
+        <v>379.11</v>
+      </c>
+      <c r="D352" t="n">
+        <v>369.94</v>
+      </c>
+      <c r="E352" t="n">
+        <v>375.59</v>
+      </c>
+      <c r="F352" t="n">
+        <v>391.12</v>
+      </c>
+      <c r="G352" t="n">
+        <v>367.52</v>
+      </c>
+      <c r="H352" t="n">
+        <v>379.21</v>
+      </c>
+      <c r="I352" t="n">
+        <v>378.38</v>
+      </c>
+      <c r="J352" t="n">
+        <v>375.58</v>
+      </c>
+      <c r="K352" t="n">
+        <v>374.51</v>
+      </c>
+      <c r="L352" t="n">
+        <v>381.01</v>
+      </c>
+      <c r="M352" t="n">
+        <v>375.66</v>
+      </c>
+      <c r="N352" t="n">
+        <v>381.66</v>
+      </c>
+      <c r="O352" t="n">
+        <v>381.66</v>
+      </c>
+      <c r="P352" t="n">
+        <v>383.05</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>387.54</v>
+      </c>
+      <c r="R352" t="n">
+        <v>385.52</v>
+      </c>
+      <c r="S352" t="n">
+        <v>376.7</v>
+      </c>
+      <c r="T352" t="n">
+        <v>363.29</v>
+      </c>
+      <c r="U352" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24697,7 +24766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B360"/>
+  <dimension ref="A1:B361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28300,6 +28369,16 @@
       </c>
       <c r="B360" t="n">
         <v>0.15</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>1.13</v>
       </c>
     </row>
   </sheetData>
@@ -28468,28 +28547,28 @@
         <v>0.0867</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03191376390975935</v>
+        <v>0.0293777237497576</v>
       </c>
       <c r="J2" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K2" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002689861944424998</v>
+        <v>0.002288970574341187</v>
       </c>
       <c r="M2" t="n">
-        <v>3.463247645608473</v>
+        <v>3.46574711749008</v>
       </c>
       <c r="N2" t="n">
-        <v>20.4228786959832</v>
+        <v>20.41859791399632</v>
       </c>
       <c r="O2" t="n">
-        <v>4.519167920755235</v>
+        <v>4.518694270914588</v>
       </c>
       <c r="P2" t="n">
-        <v>374.5023514503484</v>
+        <v>374.5285181006887</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28546,28 +28625,28 @@
         <v>0.1675</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1209479707180787</v>
+        <v>0.1186861310058355</v>
       </c>
       <c r="J3" t="n">
+        <v>351</v>
+      </c>
+      <c r="K3" t="n">
         <v>350</v>
       </c>
-      <c r="K3" t="n">
-        <v>349</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.05158876569323234</v>
+        <v>0.04994034427359062</v>
       </c>
       <c r="M3" t="n">
-        <v>2.890016887594493</v>
+        <v>2.894842178294406</v>
       </c>
       <c r="N3" t="n">
-        <v>14.40775339058414</v>
+        <v>14.40887607547915</v>
       </c>
       <c r="O3" t="n">
-        <v>3.795754653633996</v>
+        <v>3.795902537668631</v>
       </c>
       <c r="P3" t="n">
-        <v>379.7951538855554</v>
+        <v>379.8186504975145</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28624,28 +28703,28 @@
         <v>0.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03681678650080412</v>
+        <v>-0.03803341383010096</v>
       </c>
       <c r="J4" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K4" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006111157463189687</v>
+        <v>0.006554193012326515</v>
       </c>
       <c r="M4" t="n">
-        <v>2.652549915844875</v>
+        <v>2.651308035549473</v>
       </c>
       <c r="N4" t="n">
-        <v>11.92248426792442</v>
+        <v>11.90092286384614</v>
       </c>
       <c r="O4" t="n">
-        <v>3.452895056025367</v>
+        <v>3.449771421970757</v>
       </c>
       <c r="P4" t="n">
-        <v>373.0063534033619</v>
+        <v>373.0189064624271</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28702,28 +28781,28 @@
         <v>0.0907</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01083502870401634</v>
+        <v>-0.01129361578561983</v>
       </c>
       <c r="J5" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K5" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005622632181528919</v>
+        <v>0.0006146929639821996</v>
       </c>
       <c r="M5" t="n">
-        <v>2.481136403287302</v>
+        <v>2.476133114776331</v>
       </c>
       <c r="N5" t="n">
-        <v>11.28591722607445</v>
+        <v>11.25552621197613</v>
       </c>
       <c r="O5" t="n">
-        <v>3.359451923465262</v>
+        <v>3.354925664150567</v>
       </c>
       <c r="P5" t="n">
-        <v>376.6661180420252</v>
+        <v>376.6708497051922</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28780,28 +28859,28 @@
         <v>0.0612</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1214289481945842</v>
+        <v>-0.1211525670945095</v>
       </c>
       <c r="J6" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K6" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04281659493452505</v>
+        <v>0.04289296708549917</v>
       </c>
       <c r="M6" t="n">
-        <v>3.084363089480796</v>
+        <v>3.077088586362522</v>
       </c>
       <c r="N6" t="n">
-        <v>17.8274061766471</v>
+        <v>17.77725606072055</v>
       </c>
       <c r="O6" t="n">
-        <v>4.222251316140135</v>
+        <v>4.216308345071616</v>
       </c>
       <c r="P6" t="n">
-        <v>393.8308641737792</v>
+        <v>393.8280124966959</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28858,28 +28937,28 @@
         <v>0.0789</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2383395552739652</v>
+        <v>-0.2392581792633485</v>
       </c>
       <c r="J7" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K7" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1383801776369273</v>
+        <v>0.1400311731241861</v>
       </c>
       <c r="M7" t="n">
-        <v>3.250796458517252</v>
+        <v>3.246147159172402</v>
       </c>
       <c r="N7" t="n">
-        <v>19.12910742583086</v>
+        <v>19.08168123666254</v>
       </c>
       <c r="O7" t="n">
-        <v>4.37368350773474</v>
+        <v>4.368258375675887</v>
       </c>
       <c r="P7" t="n">
-        <v>375.3684273281454</v>
+        <v>375.3779056136644</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28936,28 +29015,28 @@
         <v>0.0707</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.353888678891501</v>
+        <v>-0.3534562056539527</v>
       </c>
       <c r="J8" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K8" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3064605297396058</v>
+        <v>0.3072915786822279</v>
       </c>
       <c r="M8" t="n">
-        <v>3.046965223789689</v>
+        <v>3.040642552031705</v>
       </c>
       <c r="N8" t="n">
-        <v>15.32818143223711</v>
+        <v>15.28607897232332</v>
       </c>
       <c r="O8" t="n">
-        <v>3.915122147805495</v>
+        <v>3.909741548021215</v>
       </c>
       <c r="P8" t="n">
-        <v>387.7683812832194</v>
+        <v>387.7639190605123</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29014,28 +29093,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3286690876446229</v>
+        <v>-0.3288485491317767</v>
       </c>
       <c r="J9" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K9" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2780443888531886</v>
+        <v>0.2795582831501918</v>
       </c>
       <c r="M9" t="n">
-        <v>3.056349324343319</v>
+        <v>3.048524095440174</v>
       </c>
       <c r="N9" t="n">
-        <v>15.16962127616372</v>
+        <v>15.12667291228668</v>
       </c>
       <c r="O9" t="n">
-        <v>3.89481980021717</v>
+        <v>3.889302368328629</v>
       </c>
       <c r="P9" t="n">
-        <v>387.3233295757381</v>
+        <v>387.3251812443583</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29092,28 +29171,28 @@
         <v>0.0983</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3126366397707762</v>
+        <v>-0.3124002105004108</v>
       </c>
       <c r="J10" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K10" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2663894940897068</v>
+        <v>0.2673501210996545</v>
       </c>
       <c r="M10" t="n">
-        <v>2.967730569426367</v>
+        <v>2.960544705196462</v>
       </c>
       <c r="N10" t="n">
-        <v>14.55756897206693</v>
+        <v>14.51656291884902</v>
       </c>
       <c r="O10" t="n">
-        <v>3.815438241154865</v>
+        <v>3.810060750020795</v>
       </c>
       <c r="P10" t="n">
-        <v>383.388623546839</v>
+        <v>383.3861840893945</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29170,28 +29249,28 @@
         <v>0.1068</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1983359989826329</v>
+        <v>-0.1989279131091951</v>
       </c>
       <c r="J11" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K11" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1524821211916105</v>
+        <v>0.1540610257826431</v>
       </c>
       <c r="M11" t="n">
-        <v>2.612955332980674</v>
+        <v>2.608498830666571</v>
       </c>
       <c r="N11" t="n">
-        <v>11.824797130391</v>
+        <v>11.79404472675033</v>
       </c>
       <c r="O11" t="n">
-        <v>3.438720275101044</v>
+        <v>3.434245874533495</v>
       </c>
       <c r="P11" t="n">
-        <v>380.7440208192697</v>
+        <v>380.7501281397394</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29248,28 +29327,28 @@
         <v>0.1059</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2497628574403468</v>
+        <v>-0.249057557398394</v>
       </c>
       <c r="J12" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K12" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L12" t="n">
-        <v>0.22536276132461</v>
+        <v>0.2254394129394369</v>
       </c>
       <c r="M12" t="n">
-        <v>2.587462657357584</v>
+        <v>2.584370845498293</v>
       </c>
       <c r="N12" t="n">
-        <v>11.59665088220607</v>
+        <v>11.56778123203322</v>
       </c>
       <c r="O12" t="n">
-        <v>3.405385570270431</v>
+        <v>3.401144106331459</v>
       </c>
       <c r="P12" t="n">
-        <v>386.354808994237</v>
+        <v>386.3475317673722</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29326,28 +29405,28 @@
         <v>0.1001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2277280513221935</v>
+        <v>-0.2280180071370299</v>
       </c>
       <c r="J13" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K13" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1806396036371299</v>
+        <v>0.1819672679515281</v>
       </c>
       <c r="M13" t="n">
-        <v>2.795873227895884</v>
+        <v>2.789525183344448</v>
       </c>
       <c r="N13" t="n">
-        <v>12.72200949940887</v>
+        <v>12.68646910711582</v>
       </c>
       <c r="O13" t="n">
-        <v>3.566792606727908</v>
+        <v>3.561807000262061</v>
       </c>
       <c r="P13" t="n">
-        <v>382.1406603024571</v>
+        <v>382.1436520423122</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29404,28 +29483,28 @@
         <v>0.1168</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2012027121592234</v>
+        <v>-0.2011290217874725</v>
       </c>
       <c r="J14" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K14" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1770137646256155</v>
+        <v>0.1778483213505733</v>
       </c>
       <c r="M14" t="n">
-        <v>2.450357709906088</v>
+        <v>2.443780186349691</v>
       </c>
       <c r="N14" t="n">
-        <v>10.17920482100407</v>
+        <v>10.15024974996921</v>
       </c>
       <c r="O14" t="n">
-        <v>3.190486611945593</v>
+        <v>3.18594566023484</v>
       </c>
       <c r="P14" t="n">
-        <v>386.8224145265977</v>
+        <v>386.821654195503</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29482,28 +29561,28 @@
         <v>0.1167</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.06392922544479444</v>
+        <v>-0.06439330851365402</v>
       </c>
       <c r="J15" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K15" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01703705171011682</v>
+        <v>0.01738855696571961</v>
       </c>
       <c r="M15" t="n">
-        <v>2.796220738255146</v>
+        <v>2.790456657466617</v>
       </c>
       <c r="N15" t="n">
-        <v>12.75270314581734</v>
+        <v>12.71817575567436</v>
       </c>
       <c r="O15" t="n">
-        <v>3.571092710336338</v>
+        <v>3.566255144500231</v>
       </c>
       <c r="P15" t="n">
-        <v>384.1399717679416</v>
+        <v>384.1447601382455</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29560,28 +29639,28 @@
         <v>0.1572</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.05708953889064274</v>
+        <v>-0.0563283183093747</v>
       </c>
       <c r="J16" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K16" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01595788664901965</v>
+        <v>0.01563391545289738</v>
       </c>
       <c r="M16" t="n">
-        <v>2.597578831618198</v>
+        <v>2.593631635296633</v>
       </c>
       <c r="N16" t="n">
-        <v>10.86956185809957</v>
+        <v>10.84345102205691</v>
       </c>
       <c r="O16" t="n">
-        <v>3.296901857517079</v>
+        <v>3.292939571576877</v>
       </c>
       <c r="P16" t="n">
-        <v>383.236566679816</v>
+        <v>383.2287124695018</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29638,28 +29717,28 @@
         <v>0.166</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.04453455855441998</v>
+        <v>-0.04477096499875433</v>
       </c>
       <c r="J17" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K17" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L17" t="n">
-        <v>0.00893119431963596</v>
+        <v>0.009082971939714857</v>
       </c>
       <c r="M17" t="n">
-        <v>2.709907832362293</v>
+        <v>2.703374550428458</v>
       </c>
       <c r="N17" t="n">
-        <v>11.90280258129932</v>
+        <v>11.86935987463353</v>
       </c>
       <c r="O17" t="n">
-        <v>3.450043852083523</v>
+        <v>3.445193735428174</v>
       </c>
       <c r="P17" t="n">
-        <v>389.1201101171868</v>
+        <v>389.1225493391141</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29716,28 +29795,28 @@
         <v>0.1097</v>
       </c>
       <c r="I18" t="n">
-        <v>0.02042749478577599</v>
+        <v>0.02005034338640322</v>
       </c>
       <c r="J18" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K18" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L18" t="n">
-        <v>0.002094013552636942</v>
+        <v>0.00203037286977481</v>
       </c>
       <c r="M18" t="n">
-        <v>2.604341008024944</v>
+        <v>2.5988261881924</v>
       </c>
       <c r="N18" t="n">
-        <v>10.75476723170606</v>
+        <v>10.7253190459821</v>
       </c>
       <c r="O18" t="n">
-        <v>3.279446177589451</v>
+        <v>3.274953289129801</v>
       </c>
       <c r="P18" t="n">
-        <v>385.6329945867515</v>
+        <v>385.6368860033577</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29794,28 +29873,28 @@
         <v>0.1529</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0189062249367622</v>
+        <v>-0.01989923141985573</v>
       </c>
       <c r="J19" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K19" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L19" t="n">
-        <v>0.001442759526576132</v>
+        <v>0.00160738478358291</v>
       </c>
       <c r="M19" t="n">
-        <v>2.835808145347904</v>
+        <v>2.833133892411388</v>
       </c>
       <c r="N19" t="n">
-        <v>13.37979053434827</v>
+        <v>13.34993591187909</v>
       </c>
       <c r="O19" t="n">
-        <v>3.657839599319285</v>
+        <v>3.653756411130754</v>
       </c>
       <c r="P19" t="n">
-        <v>378.9047100772609</v>
+        <v>378.9149558351313</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29872,28 +29951,28 @@
         <v>0.0994</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1165574918277458</v>
+        <v>-0.1185394392333151</v>
       </c>
       <c r="J20" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K20" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04821769554827049</v>
+        <v>0.04998728428745913</v>
       </c>
       <c r="M20" t="n">
-        <v>2.94730007779475</v>
+        <v>2.95061379066482</v>
       </c>
       <c r="N20" t="n">
-        <v>14.50348002877859</v>
+        <v>14.49508212207161</v>
       </c>
       <c r="O20" t="n">
-        <v>3.808343475683173</v>
+        <v>3.807240749160947</v>
       </c>
       <c r="P20" t="n">
-        <v>369.7687660288642</v>
+        <v>369.7892155964902</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29931,7 +30010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U351"/>
+  <dimension ref="A1:U352"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67487,6 +67566,113 @@
         </is>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>-35.43347002038665,174.4306096095118</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>-35.43405259990682,174.43015904073795</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>-35.43469612481217,174.42979160675858</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>-35.43537697012844,174.4294646753089</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>-35.436080775017174,174.42930188763611</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>-35.4367171690067,174.42880443678314</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>-35.43740431235884,174.42849023678028</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>-35.43806563831051,174.42814084769475</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>-35.43873156028859,174.42780487259157</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>-35.43941846494841,174.42752413972778</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>-35.440094183162,174.42730181062404</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>-35.4407918314885,174.4270840165767</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>-35.44148737708216,174.42689223558142</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>-35.44219060027395,174.42675422933536</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>-35.442899994182135,174.42667288512592</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>-35.443599289379435,174.42665068328682</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t>-35.444275732709684,174.4267408926216</t>
+        </is>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>-35.444938080844295,174.4269779862619</t>
+        </is>
+      </c>
+      <c r="T352" t="inlineStr">
+        <is>
+          <t>-35.44553977148517,174.42741813061548</t>
+        </is>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0075/nzd0075.xlsx
+++ b/data/nzd0075/nzd0075.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U352"/>
+  <dimension ref="A1:U353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24750,6 +24750,75 @@
         <v>363.29</v>
       </c>
       <c r="U352" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>374.12</v>
+      </c>
+      <c r="C353" t="n">
+        <v>380.09</v>
+      </c>
+      <c r="D353" t="n">
+        <v>371.4</v>
+      </c>
+      <c r="E353" t="n">
+        <v>374.39</v>
+      </c>
+      <c r="F353" t="n">
+        <v>388.68</v>
+      </c>
+      <c r="G353" t="n">
+        <v>366.86</v>
+      </c>
+      <c r="H353" t="n">
+        <v>379.84</v>
+      </c>
+      <c r="I353" t="n">
+        <v>378.97</v>
+      </c>
+      <c r="J353" t="n">
+        <v>374.97</v>
+      </c>
+      <c r="K353" t="n">
+        <v>375.32</v>
+      </c>
+      <c r="L353" t="n">
+        <v>380.7</v>
+      </c>
+      <c r="M353" t="n">
+        <v>375.29</v>
+      </c>
+      <c r="N353" t="n">
+        <v>381.74</v>
+      </c>
+      <c r="O353" t="n">
+        <v>381.97</v>
+      </c>
+      <c r="P353" t="n">
+        <v>381.76</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>387.3</v>
+      </c>
+      <c r="R353" t="n">
+        <v>386.65</v>
+      </c>
+      <c r="S353" t="n">
+        <v>377.41</v>
+      </c>
+      <c r="T353" t="n">
+        <v>363.18</v>
+      </c>
+      <c r="U353" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -24766,7 +24835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B361"/>
+  <dimension ref="A1:B362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28379,6 +28448,16 @@
       </c>
       <c r="B361" t="n">
         <v>1.13</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -28547,28 +28626,28 @@
         <v>0.0867</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0293777237497576</v>
+        <v>0.02869204427535967</v>
       </c>
       <c r="J2" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K2" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002288970574341187</v>
+        <v>0.002197335654657184</v>
       </c>
       <c r="M2" t="n">
-        <v>3.46574711749008</v>
+        <v>3.459214108160686</v>
       </c>
       <c r="N2" t="n">
-        <v>20.41859791399632</v>
+        <v>20.36453103905437</v>
       </c>
       <c r="O2" t="n">
-        <v>4.518694270914588</v>
+        <v>4.512707728077941</v>
       </c>
       <c r="P2" t="n">
-        <v>374.5285181006887</v>
+        <v>374.5356193492202</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28625,28 +28704,28 @@
         <v>0.1675</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1186861310058355</v>
+        <v>0.1170172363484435</v>
       </c>
       <c r="J3" t="n">
+        <v>352</v>
+      </c>
+      <c r="K3" t="n">
         <v>351</v>
       </c>
-      <c r="K3" t="n">
-        <v>350</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.04994034427359062</v>
+        <v>0.04884097611093074</v>
       </c>
       <c r="M3" t="n">
-        <v>2.894842178294406</v>
+        <v>2.896168772452963</v>
       </c>
       <c r="N3" t="n">
-        <v>14.40887607547915</v>
+        <v>14.39084752162263</v>
       </c>
       <c r="O3" t="n">
-        <v>3.795902537668631</v>
+        <v>3.793527055607042</v>
       </c>
       <c r="P3" t="n">
-        <v>379.8186504975145</v>
+        <v>379.8360517462245</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28703,28 +28782,28 @@
         <v>0.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03803341383010096</v>
+        <v>-0.03839251383162155</v>
       </c>
       <c r="J4" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K4" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006554193012326515</v>
+        <v>0.006720215858004752</v>
       </c>
       <c r="M4" t="n">
-        <v>2.651308035549473</v>
+        <v>2.64563150462872</v>
       </c>
       <c r="N4" t="n">
-        <v>11.90092286384614</v>
+        <v>11.86819421174026</v>
       </c>
       <c r="O4" t="n">
-        <v>3.449771421970757</v>
+        <v>3.445024558945881</v>
       </c>
       <c r="P4" t="n">
-        <v>373.0189064624271</v>
+        <v>373.022625486335</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28781,28 +28860,28 @@
         <v>0.0907</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01129361578561983</v>
+        <v>-0.01244204389752695</v>
       </c>
       <c r="J5" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K5" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0006146929639821996</v>
+        <v>0.0007500720432176422</v>
       </c>
       <c r="M5" t="n">
-        <v>2.476133114776331</v>
+        <v>2.474285061379435</v>
       </c>
       <c r="N5" t="n">
-        <v>11.25552621197613</v>
+        <v>11.23460422946161</v>
       </c>
       <c r="O5" t="n">
-        <v>3.354925664150567</v>
+        <v>3.351806114539087</v>
       </c>
       <c r="P5" t="n">
-        <v>376.6708497051922</v>
+        <v>376.6827434160988</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28859,28 +28938,28 @@
         <v>0.0612</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1211525670945095</v>
+        <v>-0.1222872755126326</v>
       </c>
       <c r="J6" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K6" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04289296708549917</v>
+        <v>0.04391073140600898</v>
       </c>
       <c r="M6" t="n">
-        <v>3.077088586362522</v>
+        <v>3.073217708685881</v>
       </c>
       <c r="N6" t="n">
-        <v>17.77725606072055</v>
+        <v>17.73754390235777</v>
       </c>
       <c r="O6" t="n">
-        <v>4.216308345071616</v>
+        <v>4.211596360331527</v>
       </c>
       <c r="P6" t="n">
-        <v>393.8280124966959</v>
+        <v>393.8397641194128</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28937,28 +29016,28 @@
         <v>0.0789</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2392581792633485</v>
+        <v>-0.2405379539795794</v>
       </c>
       <c r="J7" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K7" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1400311731241861</v>
+        <v>0.1420210556986493</v>
       </c>
       <c r="M7" t="n">
-        <v>3.246147159172402</v>
+        <v>3.24333278590932</v>
       </c>
       <c r="N7" t="n">
-        <v>19.08168123666254</v>
+        <v>19.04119894837944</v>
       </c>
       <c r="O7" t="n">
-        <v>4.368258375675887</v>
+        <v>4.363622227963764</v>
       </c>
       <c r="P7" t="n">
-        <v>375.3779056136644</v>
+        <v>375.3911596174135</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29015,28 +29094,28 @@
         <v>0.0707</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3534562056539527</v>
+        <v>-0.3526444400129941</v>
       </c>
       <c r="J8" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K8" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3072915786822279</v>
+        <v>0.3076147608542701</v>
       </c>
       <c r="M8" t="n">
-        <v>3.040642552031705</v>
+        <v>3.036386937983549</v>
       </c>
       <c r="N8" t="n">
-        <v>15.28607897232332</v>
+        <v>15.24817555980327</v>
       </c>
       <c r="O8" t="n">
-        <v>3.909741548021215</v>
+        <v>3.904891235335918</v>
       </c>
       <c r="P8" t="n">
-        <v>387.7639190605123</v>
+        <v>387.7555119989316</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29093,28 +29172,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3288485491317767</v>
+        <v>-0.3286641963911674</v>
       </c>
       <c r="J9" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K9" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2795582831501918</v>
+        <v>0.2806347042382726</v>
       </c>
       <c r="M9" t="n">
-        <v>3.048524095440174</v>
+        <v>3.040757724983851</v>
       </c>
       <c r="N9" t="n">
-        <v>15.12667291228668</v>
+        <v>15.08398425484918</v>
       </c>
       <c r="O9" t="n">
-        <v>3.889302368328629</v>
+        <v>3.883810532820722</v>
       </c>
       <c r="P9" t="n">
-        <v>387.3251812443583</v>
+        <v>387.3232719927657</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29171,28 +29250,28 @@
         <v>0.0983</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3124002105004108</v>
+        <v>-0.3125054668321566</v>
       </c>
       <c r="J10" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K10" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2673501210996545</v>
+        <v>0.2687521616651857</v>
       </c>
       <c r="M10" t="n">
-        <v>2.960544705196462</v>
+        <v>2.952597154963342</v>
       </c>
       <c r="N10" t="n">
-        <v>14.51656291884902</v>
+        <v>14.47541553845638</v>
       </c>
       <c r="O10" t="n">
-        <v>3.810060750020795</v>
+        <v>3.804657085527733</v>
       </c>
       <c r="P10" t="n">
-        <v>383.3861840893945</v>
+        <v>383.3872741779842</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29249,28 +29328,28 @@
         <v>0.1068</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1989279131091951</v>
+        <v>-0.1990361072441433</v>
       </c>
       <c r="J11" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K11" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1540610257826431</v>
+        <v>0.1550485833665017</v>
       </c>
       <c r="M11" t="n">
-        <v>2.608498830666571</v>
+        <v>2.601628633604387</v>
       </c>
       <c r="N11" t="n">
-        <v>11.79404472675033</v>
+        <v>11.76063702872626</v>
       </c>
       <c r="O11" t="n">
-        <v>3.434245874533495</v>
+        <v>3.429378519313121</v>
       </c>
       <c r="P11" t="n">
-        <v>380.7501281397394</v>
+        <v>380.7512486537268</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29327,28 +29406,28 @@
         <v>0.1059</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.249057557398394</v>
+        <v>-0.2485263871482055</v>
       </c>
       <c r="J12" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K12" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2254394129394369</v>
+        <v>0.2257894829720691</v>
       </c>
       <c r="M12" t="n">
-        <v>2.584370845498293</v>
+        <v>2.580220123193579</v>
       </c>
       <c r="N12" t="n">
-        <v>11.56778123203322</v>
+        <v>11.53728292301666</v>
       </c>
       <c r="O12" t="n">
-        <v>3.401144106331459</v>
+        <v>3.396657610507226</v>
       </c>
       <c r="P12" t="n">
-        <v>386.3475317673722</v>
+        <v>386.3420306956617</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29405,28 +29484,28 @@
         <v>0.1001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2280180071370299</v>
+        <v>-0.2285072997718507</v>
       </c>
       <c r="J13" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K13" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1819672679515281</v>
+        <v>0.1835515302147758</v>
       </c>
       <c r="M13" t="n">
-        <v>2.789525183344448</v>
+        <v>2.784307081830941</v>
       </c>
       <c r="N13" t="n">
-        <v>12.68646910711582</v>
+        <v>12.65243453788347</v>
       </c>
       <c r="O13" t="n">
-        <v>3.561807000262061</v>
+        <v>3.557026080573978</v>
       </c>
       <c r="P13" t="n">
-        <v>382.1436520423122</v>
+        <v>382.1487194079462</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29483,28 +29562,28 @@
         <v>0.1168</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2011290217874725</v>
+        <v>-0.2010016402412811</v>
       </c>
       <c r="J14" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K14" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1778483213505733</v>
+        <v>0.1786096619575424</v>
       </c>
       <c r="M14" t="n">
-        <v>2.443780186349691</v>
+        <v>2.43752831365565</v>
       </c>
       <c r="N14" t="n">
-        <v>10.15024974996921</v>
+        <v>10.12154980809501</v>
       </c>
       <c r="O14" t="n">
-        <v>3.18594566023484</v>
+        <v>3.181438323792403</v>
       </c>
       <c r="P14" t="n">
-        <v>386.821654195503</v>
+        <v>386.8203349668377</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29561,28 +29640,28 @@
         <v>0.1167</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.06439330851365402</v>
+        <v>-0.06467097068969596</v>
       </c>
       <c r="J15" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K15" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01738855696571961</v>
+        <v>0.01764728816378169</v>
       </c>
       <c r="M15" t="n">
-        <v>2.790456657466617</v>
+        <v>2.783843168783806</v>
       </c>
       <c r="N15" t="n">
-        <v>12.71817575567436</v>
+        <v>12.68269073903627</v>
       </c>
       <c r="O15" t="n">
-        <v>3.566255144500231</v>
+        <v>3.561276560313207</v>
       </c>
       <c r="P15" t="n">
-        <v>384.1447601382455</v>
+        <v>384.1476357502385</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29639,28 +29718,28 @@
         <v>0.1572</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0563283183093747</v>
+        <v>-0.05632080202499624</v>
       </c>
       <c r="J16" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K16" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01563391545289738</v>
+        <v>0.01572979911656436</v>
       </c>
       <c r="M16" t="n">
-        <v>2.593631635296633</v>
+        <v>2.586297079556114</v>
       </c>
       <c r="N16" t="n">
-        <v>10.84345102205691</v>
+        <v>10.81264623696722</v>
       </c>
       <c r="O16" t="n">
-        <v>3.292939571576877</v>
+        <v>3.28825884579776</v>
       </c>
       <c r="P16" t="n">
-        <v>383.2287124695018</v>
+        <v>383.2286346270034</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29717,28 +29796,28 @@
         <v>0.166</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.04477096499875433</v>
+        <v>-0.04514438839704336</v>
       </c>
       <c r="J17" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K17" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L17" t="n">
-        <v>0.009082971939714857</v>
+        <v>0.009292266129525051</v>
       </c>
       <c r="M17" t="n">
-        <v>2.703374550428458</v>
+        <v>2.697550459924992</v>
       </c>
       <c r="N17" t="n">
-        <v>11.86935987463353</v>
+        <v>11.83680882822805</v>
       </c>
       <c r="O17" t="n">
-        <v>3.445193735428174</v>
+        <v>3.44046636783853</v>
       </c>
       <c r="P17" t="n">
-        <v>389.1225493391141</v>
+        <v>389.1264167034698</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29795,28 +29874,28 @@
         <v>0.1097</v>
       </c>
       <c r="I18" t="n">
-        <v>0.02005034338640322</v>
+        <v>0.02033247998415594</v>
       </c>
       <c r="J18" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K18" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L18" t="n">
-        <v>0.00203037286977481</v>
+        <v>0.002101205906940851</v>
       </c>
       <c r="M18" t="n">
-        <v>2.5988261881924</v>
+        <v>2.592773793173128</v>
       </c>
       <c r="N18" t="n">
-        <v>10.7253190459821</v>
+        <v>10.6955165472803</v>
       </c>
       <c r="O18" t="n">
-        <v>3.274953289129801</v>
+        <v>3.270400059209928</v>
       </c>
       <c r="P18" t="n">
-        <v>385.6368860033577</v>
+        <v>385.6339640519572</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29873,28 +29952,28 @@
         <v>0.1529</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.01989923141985573</v>
+        <v>-0.02046797251279627</v>
       </c>
       <c r="J19" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K19" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L19" t="n">
-        <v>0.00160738478358291</v>
+        <v>0.001711106302140886</v>
       </c>
       <c r="M19" t="n">
-        <v>2.833133892411388</v>
+        <v>2.82814877815103</v>
       </c>
       <c r="N19" t="n">
-        <v>13.34993591187909</v>
+        <v>13.31472101587539</v>
       </c>
       <c r="O19" t="n">
-        <v>3.653756411130754</v>
+        <v>3.648934230138355</v>
       </c>
       <c r="P19" t="n">
-        <v>378.9149558351313</v>
+        <v>378.9208460097709</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29951,28 +30030,28 @@
         <v>0.0994</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1185394392333151</v>
+        <v>-0.1205593913290505</v>
       </c>
       <c r="J20" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K20" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04998728428745913</v>
+        <v>0.05181855258566959</v>
       </c>
       <c r="M20" t="n">
-        <v>2.95061379066482</v>
+        <v>2.954182883714283</v>
       </c>
       <c r="N20" t="n">
-        <v>14.49508212207161</v>
+        <v>14.48810020842055</v>
       </c>
       <c r="O20" t="n">
-        <v>3.807240749160947</v>
+        <v>3.806323713036051</v>
       </c>
       <c r="P20" t="n">
-        <v>369.7892155964902</v>
+        <v>369.8101352570446</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30010,7 +30089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U352"/>
+  <dimension ref="A1:U353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67673,6 +67752,113 @@
         </is>
       </c>
     </row>
+    <row r="353">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:06+00:00</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>-35.43348726307206,174.430637177731</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>-35.43405667729005,174.43016861694306</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>-35.43470090685315,174.42980658964458</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>-35.43537273726633,174.4294525110713</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>-35.43607382019859,174.42927638938534</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>-35.43671495034536,174.42879769106125</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>-35.437406722030076,174.42849652087185</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>-35.438067537310914,174.42814691846738</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>-35.43872982278101,174.42779849732958</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>-35.439420733769836,174.42753262077872</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>-35.44009348493387,174.4272985040452</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>-35.44079107348743,174.42708004735633</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>-35.441487532219206,174.4268930962251</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>-35.44219094791097,174.42675761778017</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>-35.44289899763733,174.4266587265941</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>-35.44359937160442,174.4266480413032</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t>-35.44427294733221,174.42675286667628</t>
+        </is>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>-35.44493468156047,174.42698461366783</t>
+        </is>
+      </c>
+      <c r="T353" t="inlineStr">
+        <is>
+          <t>-35.44554042292862,174.42741721697237</t>
+        </is>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0075/nzd0075.xlsx
+++ b/data/nzd0075/nzd0075.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U353"/>
+  <dimension ref="A1:U354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24821,6 +24821,75 @@
       <c r="U353" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>375.77</v>
+      </c>
+      <c r="C354" t="n">
+        <v>381.52</v>
+      </c>
+      <c r="D354" t="n">
+        <v>373.18</v>
+      </c>
+      <c r="E354" t="n">
+        <v>374.27</v>
+      </c>
+      <c r="F354" t="n">
+        <v>388.18</v>
+      </c>
+      <c r="G354" t="n">
+        <v>369.12</v>
+      </c>
+      <c r="H354" t="n">
+        <v>380.88</v>
+      </c>
+      <c r="I354" t="n">
+        <v>380.87</v>
+      </c>
+      <c r="J354" t="n">
+        <v>377.7</v>
+      </c>
+      <c r="K354" t="n">
+        <v>375.07</v>
+      </c>
+      <c r="L354" t="n">
+        <v>379.74</v>
+      </c>
+      <c r="M354" t="n">
+        <v>374.15</v>
+      </c>
+      <c r="N354" t="n">
+        <v>382.11</v>
+      </c>
+      <c r="O354" t="n">
+        <v>380.74</v>
+      </c>
+      <c r="P354" t="n">
+        <v>382.29</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>387.51</v>
+      </c>
+      <c r="R354" t="n">
+        <v>387.74</v>
+      </c>
+      <c r="S354" t="n">
+        <v>376.4</v>
+      </c>
+      <c r="T354" t="n">
+        <v>362.82</v>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -24835,7 +24904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B362"/>
+  <dimension ref="A1:B363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28458,6 +28527,16 @@
       </c>
       <c r="B362" t="n">
         <v>0.71</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>0.88</v>
       </c>
     </row>
   </sheetData>
@@ -28626,28 +28705,28 @@
         <v>0.0867</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02869204427535967</v>
+        <v>0.02896519557648719</v>
       </c>
       <c r="J2" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K2" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002197335654657184</v>
+        <v>0.002253954882876386</v>
       </c>
       <c r="M2" t="n">
-        <v>3.459214108160686</v>
+        <v>3.450748057207988</v>
       </c>
       <c r="N2" t="n">
-        <v>20.36453103905437</v>
+        <v>20.30745933607895</v>
       </c>
       <c r="O2" t="n">
-        <v>4.512707728077941</v>
+        <v>4.506379848179574</v>
       </c>
       <c r="P2" t="n">
-        <v>374.5356193492202</v>
+        <v>374.5327722293604</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28704,28 +28783,28 @@
         <v>0.1675</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1170172363484435</v>
+        <v>0.1161839773241342</v>
       </c>
       <c r="J3" t="n">
+        <v>353</v>
+      </c>
+      <c r="K3" t="n">
         <v>352</v>
       </c>
-      <c r="K3" t="n">
-        <v>351</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.04884097611093074</v>
+        <v>0.04846696436196263</v>
       </c>
       <c r="M3" t="n">
-        <v>2.896168772452963</v>
+        <v>2.892645498787738</v>
       </c>
       <c r="N3" t="n">
-        <v>14.39084752162263</v>
+        <v>14.35563776463163</v>
       </c>
       <c r="O3" t="n">
-        <v>3.793527055607042</v>
+        <v>3.788883445638256</v>
       </c>
       <c r="P3" t="n">
-        <v>379.8360517462245</v>
+        <v>379.8447954858338</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28782,28 +28861,28 @@
         <v>0.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03839251383162155</v>
+        <v>-0.03771059687649532</v>
       </c>
       <c r="J4" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K4" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006720215858004752</v>
+        <v>0.006525554372440734</v>
       </c>
       <c r="M4" t="n">
-        <v>2.64563150462872</v>
+        <v>2.641254981959631</v>
       </c>
       <c r="N4" t="n">
-        <v>11.86819421174026</v>
+        <v>11.83842606132665</v>
       </c>
       <c r="O4" t="n">
-        <v>3.445024558945881</v>
+        <v>3.440701390897887</v>
       </c>
       <c r="P4" t="n">
-        <v>373.022625486335</v>
+        <v>373.0155177065161</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28860,28 +28939,28 @@
         <v>0.0907</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01244204389752695</v>
+        <v>-0.01365183159195428</v>
       </c>
       <c r="J5" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K5" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0007500720432176422</v>
+        <v>0.000907861648098196</v>
       </c>
       <c r="M5" t="n">
-        <v>2.474285061379435</v>
+        <v>2.472780627482115</v>
       </c>
       <c r="N5" t="n">
-        <v>11.23460422946161</v>
+        <v>11.21490454156252</v>
       </c>
       <c r="O5" t="n">
-        <v>3.351806114539087</v>
+        <v>3.348866157606559</v>
       </c>
       <c r="P5" t="n">
-        <v>376.6827434160988</v>
+        <v>376.6953533160212</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28938,28 +29017,28 @@
         <v>0.0612</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1222872755126326</v>
+        <v>-0.1236957836982817</v>
       </c>
       <c r="J6" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K6" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04391073140600898</v>
+        <v>0.04512520925678465</v>
       </c>
       <c r="M6" t="n">
-        <v>3.073217708685881</v>
+        <v>3.070443841298506</v>
       </c>
       <c r="N6" t="n">
-        <v>17.73754390235777</v>
+        <v>17.70373325359266</v>
       </c>
       <c r="O6" t="n">
-        <v>4.211596360331527</v>
+        <v>4.207580451232354</v>
       </c>
       <c r="P6" t="n">
-        <v>393.8397641194128</v>
+        <v>393.8544453294654</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29016,28 +29095,28 @@
         <v>0.0789</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2405379539795794</v>
+        <v>-0.2404745520455134</v>
       </c>
       <c r="J7" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K7" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1420210556986493</v>
+        <v>0.142759715931034</v>
       </c>
       <c r="M7" t="n">
-        <v>3.24333278590932</v>
+        <v>3.23444390535465</v>
       </c>
       <c r="N7" t="n">
-        <v>19.04119894837944</v>
+        <v>18.98729118053478</v>
       </c>
       <c r="O7" t="n">
-        <v>4.363622227963764</v>
+        <v>4.357440898111503</v>
       </c>
       <c r="P7" t="n">
-        <v>375.3911596174135</v>
+        <v>375.3904987642347</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29094,28 +29173,28 @@
         <v>0.0707</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3526444400129941</v>
+        <v>-0.3512033671901886</v>
       </c>
       <c r="J8" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K8" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3076147608542701</v>
+        <v>0.3070308867738647</v>
       </c>
       <c r="M8" t="n">
-        <v>3.036386937983549</v>
+        <v>3.03548115416466</v>
       </c>
       <c r="N8" t="n">
-        <v>15.24817555980327</v>
+        <v>15.22218579371911</v>
       </c>
       <c r="O8" t="n">
-        <v>3.904891235335918</v>
+        <v>3.90156196845816</v>
       </c>
       <c r="P8" t="n">
-        <v>387.7555119989316</v>
+        <v>387.7404913600541</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29172,28 +29251,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3286641963911674</v>
+        <v>-0.3273452351358666</v>
       </c>
       <c r="J9" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K9" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2806347042382726</v>
+        <v>0.2801459551712512</v>
       </c>
       <c r="M9" t="n">
-        <v>3.040757724983851</v>
+        <v>3.038485458420205</v>
       </c>
       <c r="N9" t="n">
-        <v>15.08398425484918</v>
+        <v>15.0556671768698</v>
       </c>
       <c r="O9" t="n">
-        <v>3.883810532820722</v>
+        <v>3.880163292552234</v>
       </c>
       <c r="P9" t="n">
-        <v>387.3232719927657</v>
+        <v>387.3095241512995</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29250,28 +29329,28 @@
         <v>0.0983</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3125054668321566</v>
+        <v>-0.3109889805696539</v>
       </c>
       <c r="J10" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K10" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2687521616651857</v>
+        <v>0.2678745523920009</v>
       </c>
       <c r="M10" t="n">
-        <v>2.952597154963342</v>
+        <v>2.952304450665699</v>
       </c>
       <c r="N10" t="n">
-        <v>14.47541553845638</v>
+        <v>14.45346286569422</v>
       </c>
       <c r="O10" t="n">
-        <v>3.804657085527733</v>
+        <v>3.801771016999079</v>
       </c>
       <c r="P10" t="n">
-        <v>383.3872741779842</v>
+        <v>383.371467487197</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29328,28 +29407,28 @@
         <v>0.1068</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1990361072441433</v>
+        <v>-0.1992700393052083</v>
       </c>
       <c r="J11" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K11" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1550485833665017</v>
+        <v>0.1562166239250128</v>
       </c>
       <c r="M11" t="n">
-        <v>2.601628633604387</v>
+        <v>2.595407587735794</v>
       </c>
       <c r="N11" t="n">
-        <v>11.76063702872626</v>
+        <v>11.72777418806283</v>
       </c>
       <c r="O11" t="n">
-        <v>3.429378519313121</v>
+        <v>3.42458379778665</v>
       </c>
       <c r="P11" t="n">
-        <v>380.7512486537268</v>
+        <v>380.7536869822799</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29406,28 +29485,28 @@
         <v>0.1059</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2485263871482055</v>
+        <v>-0.2485345597505369</v>
       </c>
       <c r="J12" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K12" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2257894829720691</v>
+        <v>0.2269529556660665</v>
       </c>
       <c r="M12" t="n">
-        <v>2.580220123193579</v>
+        <v>2.572941177979166</v>
       </c>
       <c r="N12" t="n">
-        <v>11.53728292301666</v>
+        <v>11.50459995538148</v>
       </c>
       <c r="O12" t="n">
-        <v>3.396657610507226</v>
+        <v>3.391843150173881</v>
       </c>
       <c r="P12" t="n">
-        <v>386.3420306956617</v>
+        <v>386.3421158806062</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29484,28 +29563,28 @@
         <v>0.1001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2285072997718507</v>
+        <v>-0.2296326977145461</v>
       </c>
       <c r="J13" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K13" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1835515302147758</v>
+        <v>0.1858967113520007</v>
       </c>
       <c r="M13" t="n">
-        <v>2.784307081830941</v>
+        <v>2.782548702389583</v>
       </c>
       <c r="N13" t="n">
-        <v>12.65243453788347</v>
+        <v>12.62708556659286</v>
       </c>
       <c r="O13" t="n">
-        <v>3.557026080573978</v>
+        <v>3.553461068675561</v>
       </c>
       <c r="P13" t="n">
-        <v>382.1487194079462</v>
+        <v>382.1604496937606</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29562,28 +29641,28 @@
         <v>0.1168</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2010016402412811</v>
+        <v>-0.2006378458289397</v>
       </c>
       <c r="J14" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K14" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1786096619575424</v>
+        <v>0.1790275963417557</v>
       </c>
       <c r="M14" t="n">
-        <v>2.43752831365565</v>
+        <v>2.432565898398482</v>
       </c>
       <c r="N14" t="n">
-        <v>10.12154980809501</v>
+        <v>10.09397340409754</v>
       </c>
       <c r="O14" t="n">
-        <v>3.181438323792403</v>
+        <v>3.17710141545679</v>
       </c>
       <c r="P14" t="n">
-        <v>386.8203349668377</v>
+        <v>386.8165430526423</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29640,28 +29719,28 @@
         <v>0.1167</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.06467097068969596</v>
+        <v>-0.06565701818304417</v>
       </c>
       <c r="J15" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K15" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01764728816378169</v>
+        <v>0.01828602204248064</v>
       </c>
       <c r="M15" t="n">
-        <v>2.783843168783806</v>
+        <v>2.780603338144697</v>
       </c>
       <c r="N15" t="n">
-        <v>12.68269073903627</v>
+        <v>12.65481823793455</v>
       </c>
       <c r="O15" t="n">
-        <v>3.561276560313207</v>
+        <v>3.557361134033843</v>
       </c>
       <c r="P15" t="n">
-        <v>384.1476357502385</v>
+        <v>384.1579135537466</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29718,28 +29797,28 @@
         <v>0.1572</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.05632080202499624</v>
+        <v>-0.05599475363429413</v>
       </c>
       <c r="J16" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K16" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01572979911656436</v>
+        <v>0.01565079161689908</v>
       </c>
       <c r="M16" t="n">
-        <v>2.586297079556114</v>
+        <v>2.580407554898251</v>
       </c>
       <c r="N16" t="n">
-        <v>10.81264623696722</v>
+        <v>10.78289631086736</v>
       </c>
       <c r="O16" t="n">
-        <v>3.28825884579776</v>
+        <v>3.283732070505656</v>
       </c>
       <c r="P16" t="n">
-        <v>383.2286346270034</v>
+        <v>383.2252361484145</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29796,28 +29875,28 @@
         <v>0.166</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.04514438839704336</v>
+        <v>-0.04538532634914384</v>
       </c>
       <c r="J17" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K17" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L17" t="n">
-        <v>0.009292266129525051</v>
+        <v>0.009451791201583348</v>
       </c>
       <c r="M17" t="n">
-        <v>2.697550459924992</v>
+        <v>2.691087101157273</v>
       </c>
       <c r="N17" t="n">
-        <v>11.83680882822805</v>
+        <v>11.80375776799875</v>
       </c>
       <c r="O17" t="n">
-        <v>3.44046636783853</v>
+        <v>3.435659728203413</v>
       </c>
       <c r="P17" t="n">
-        <v>389.1264167034698</v>
+        <v>389.1289280560629</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29874,28 +29953,28 @@
         <v>0.1097</v>
       </c>
       <c r="I18" t="n">
-        <v>0.02033247998415594</v>
+        <v>0.02124283891888901</v>
       </c>
       <c r="J18" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K18" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L18" t="n">
-        <v>0.002101205906940851</v>
+        <v>0.002306751269838481</v>
       </c>
       <c r="M18" t="n">
-        <v>2.592773793173128</v>
+        <v>2.589650630392213</v>
       </c>
       <c r="N18" t="n">
-        <v>10.6955165472803</v>
+        <v>10.67208418052215</v>
       </c>
       <c r="O18" t="n">
-        <v>3.270400059209928</v>
+        <v>3.266815602467049</v>
       </c>
       <c r="P18" t="n">
-        <v>385.6339640519572</v>
+        <v>385.6244751679875</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29952,28 +30031,28 @@
         <v>0.1529</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.02046797251279627</v>
+        <v>-0.02162056300313392</v>
       </c>
       <c r="J19" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K19" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L19" t="n">
-        <v>0.001711106302140886</v>
+        <v>0.001919850291460912</v>
       </c>
       <c r="M19" t="n">
-        <v>2.82814877815103</v>
+        <v>2.826246466093889</v>
       </c>
       <c r="N19" t="n">
-        <v>13.31472101587539</v>
+        <v>13.28800911182682</v>
       </c>
       <c r="O19" t="n">
-        <v>3.648934230138355</v>
+        <v>3.645272158814321</v>
       </c>
       <c r="P19" t="n">
-        <v>378.9208460097709</v>
+        <v>378.9328597298655</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30030,28 +30109,28 @@
         <v>0.0994</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1205593913290505</v>
+        <v>-0.1227679553580488</v>
       </c>
       <c r="J20" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K20" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05181855258566959</v>
+        <v>0.05382414931147583</v>
       </c>
       <c r="M20" t="n">
-        <v>2.954182883714283</v>
+        <v>2.958900293679858</v>
       </c>
       <c r="N20" t="n">
-        <v>14.48810020842055</v>
+        <v>14.48747154602612</v>
       </c>
       <c r="O20" t="n">
-        <v>3.806323713036051</v>
+        <v>3.806241130830537</v>
       </c>
       <c r="P20" t="n">
-        <v>369.8101352570446</v>
+        <v>369.8331556361625</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30089,7 +30168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U353"/>
+  <dimension ref="A1:U354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67859,6 +67938,113 @@
         </is>
       </c>
     </row>
+    <row r="354">
+      <c r="A354" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>-35.433496294952256,174.43065161823142</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>-35.43406262693969,174.43018259038695</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>-35.43470673701015,174.4298248564532</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>-35.43537231398005,174.42945129464763</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>-35.43607239503017,174.4292711643345</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>-35.43672254757804,174.42882079004977</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>-35.4374106998993,174.42850689461113</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>-35.4380736527338,174.428166468415</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>-35.43873759883679,174.42782702924188</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>-35.43942003351638,174.42753000317038</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>-35.440091322678384,174.42728826431753</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>-35.44078873802383,174.42706781786697</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>-35.441488249727904,174.42689707670218</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>-35.44218956857646,174.42674417330568</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>-35.44289940707067,174.42666454366528</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>-35.443599299657556,174.42665035303887</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t>-35.444270260551036,174.4267644168698</t>
+        </is>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>-35.4449395171613,174.42697518594937</t>
+        </is>
+      </c>
+      <c r="T354" t="inlineStr">
+        <is>
+          <t>-35.44554255492531,174.42741422686768</t>
+        </is>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0075/nzd0075.xlsx
+++ b/data/nzd0075/nzd0075.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U354"/>
+  <dimension ref="A1:U355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24888,6 +24888,75 @@
         <v>362.82</v>
       </c>
       <c r="U354" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:10+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>374.65</v>
+      </c>
+      <c r="C355" t="n">
+        <v>378.24</v>
+      </c>
+      <c r="D355" t="n">
+        <v>370.47</v>
+      </c>
+      <c r="E355" t="n">
+        <v>371.57</v>
+      </c>
+      <c r="F355" t="n">
+        <v>385.29</v>
+      </c>
+      <c r="G355" t="n">
+        <v>367.84</v>
+      </c>
+      <c r="H355" t="n">
+        <v>378.03</v>
+      </c>
+      <c r="I355" t="n">
+        <v>377.88</v>
+      </c>
+      <c r="J355" t="n">
+        <v>375.16</v>
+      </c>
+      <c r="K355" t="n">
+        <v>372.42</v>
+      </c>
+      <c r="L355" t="n">
+        <v>376.95</v>
+      </c>
+      <c r="M355" t="n">
+        <v>371.68</v>
+      </c>
+      <c r="N355" t="n">
+        <v>381.14</v>
+      </c>
+      <c r="O355" t="n">
+        <v>378.82</v>
+      </c>
+      <c r="P355" t="n">
+        <v>377.81</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>383.02</v>
+      </c>
+      <c r="R355" t="n">
+        <v>385.99</v>
+      </c>
+      <c r="S355" t="n">
+        <v>372.09</v>
+      </c>
+      <c r="T355" t="n">
+        <v>362.9</v>
+      </c>
+      <c r="U355" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -24904,7 +24973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B363"/>
+  <dimension ref="A1:B364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28537,6 +28606,16 @@
       </c>
       <c r="B363" t="n">
         <v>0.88</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>0.97</v>
       </c>
     </row>
   </sheetData>
@@ -28705,28 +28784,28 @@
         <v>0.0867</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02896519557648719</v>
+        <v>0.02858531534495889</v>
       </c>
       <c r="J2" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K2" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002253954882876386</v>
+        <v>0.002209610764478454</v>
       </c>
       <c r="M2" t="n">
-        <v>3.450748057207988</v>
+        <v>3.442831403776634</v>
       </c>
       <c r="N2" t="n">
-        <v>20.30745933607895</v>
+        <v>20.2512991083285</v>
       </c>
       <c r="O2" t="n">
-        <v>4.506379848179574</v>
+        <v>4.500144343054843</v>
       </c>
       <c r="P2" t="n">
-        <v>374.5327722293604</v>
+        <v>374.536738992472</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28783,28 +28862,28 @@
         <v>0.1675</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1161839773241342</v>
+        <v>0.1134469495672261</v>
       </c>
       <c r="J3" t="n">
+        <v>354</v>
+      </c>
+      <c r="K3" t="n">
         <v>353</v>
       </c>
-      <c r="K3" t="n">
-        <v>352</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.04846696436196263</v>
+        <v>0.04641547196207008</v>
       </c>
       <c r="M3" t="n">
-        <v>2.892645498787738</v>
+        <v>2.899802517220041</v>
       </c>
       <c r="N3" t="n">
-        <v>14.35563776463163</v>
+        <v>14.37668725720784</v>
       </c>
       <c r="O3" t="n">
-        <v>3.788883445638256</v>
+        <v>3.791660224388235</v>
       </c>
       <c r="P3" t="n">
-        <v>379.8447954858338</v>
+        <v>379.8735679420296</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28861,28 +28940,28 @@
         <v>0.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03771059687649532</v>
+        <v>-0.03860404507572667</v>
       </c>
       <c r="J4" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K4" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006525554372440734</v>
+        <v>0.0068770371550122</v>
       </c>
       <c r="M4" t="n">
-        <v>2.641254981959631</v>
+        <v>2.638375249869819</v>
       </c>
       <c r="N4" t="n">
-        <v>11.83842606132665</v>
+        <v>11.81165231117896</v>
       </c>
       <c r="O4" t="n">
-        <v>3.440701390897887</v>
+        <v>3.436808448426965</v>
       </c>
       <c r="P4" t="n">
-        <v>373.0155177065161</v>
+        <v>373.0248472189903</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28939,28 +29018,28 @@
         <v>0.0907</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01365183159195428</v>
+        <v>-0.01641077396547192</v>
       </c>
       <c r="J5" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K5" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000907861648098196</v>
+        <v>0.001312507561195386</v>
       </c>
       <c r="M5" t="n">
-        <v>2.472780627482115</v>
+        <v>2.478839000415126</v>
       </c>
       <c r="N5" t="n">
-        <v>11.21490454156252</v>
+        <v>11.24680843104743</v>
       </c>
       <c r="O5" t="n">
-        <v>3.348866157606559</v>
+        <v>3.353626161492577</v>
       </c>
       <c r="P5" t="n">
-        <v>376.6953533160212</v>
+        <v>376.7241625825368</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29017,28 +29096,28 @@
         <v>0.0612</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1236957836982817</v>
+        <v>-0.1267495863725924</v>
       </c>
       <c r="J6" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K6" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04512520925678465</v>
+        <v>0.04737091637508306</v>
       </c>
       <c r="M6" t="n">
-        <v>3.070443841298506</v>
+        <v>3.074591261684323</v>
       </c>
       <c r="N6" t="n">
-        <v>17.70373325359266</v>
+        <v>17.7316244793363</v>
       </c>
       <c r="O6" t="n">
-        <v>4.207580451232354</v>
+        <v>4.210893548801288</v>
       </c>
       <c r="P6" t="n">
-        <v>393.8544453294654</v>
+        <v>393.8863335689497</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29095,28 +29174,28 @@
         <v>0.0789</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2404745520455134</v>
+        <v>-0.241148013683711</v>
       </c>
       <c r="J7" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K7" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L7" t="n">
-        <v>0.142759715931034</v>
+        <v>0.1442274013395602</v>
       </c>
       <c r="M7" t="n">
-        <v>3.23444390535465</v>
+        <v>3.228663264720352</v>
       </c>
       <c r="N7" t="n">
-        <v>18.98729118053478</v>
+        <v>18.937443472616</v>
       </c>
       <c r="O7" t="n">
-        <v>4.357440898111503</v>
+        <v>4.351717301550734</v>
       </c>
       <c r="P7" t="n">
-        <v>375.3904987642347</v>
+        <v>375.3975311459216</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29173,28 +29252,28 @@
         <v>0.0707</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3512033671901886</v>
+        <v>-0.3514254437809355</v>
       </c>
       <c r="J8" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K8" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3070308867738647</v>
+        <v>0.3086899051765881</v>
       </c>
       <c r="M8" t="n">
-        <v>3.03548115416466</v>
+        <v>3.027873484994201</v>
       </c>
       <c r="N8" t="n">
-        <v>15.22218579371911</v>
+        <v>15.17959724396666</v>
       </c>
       <c r="O8" t="n">
-        <v>3.90156196845816</v>
+        <v>3.896100261025973</v>
       </c>
       <c r="P8" t="n">
-        <v>387.7404913600541</v>
+        <v>387.7428103152273</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29251,28 +29330,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3273452351358666</v>
+        <v>-0.3277680967500178</v>
       </c>
       <c r="J9" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K9" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2801459551712512</v>
+        <v>0.2819708213300335</v>
       </c>
       <c r="M9" t="n">
-        <v>3.038485458420205</v>
+        <v>3.031960505156131</v>
       </c>
       <c r="N9" t="n">
-        <v>15.0556671768698</v>
+        <v>15.01463073857322</v>
       </c>
       <c r="O9" t="n">
-        <v>3.880163292552234</v>
+        <v>3.874871706079211</v>
       </c>
       <c r="P9" t="n">
-        <v>387.3095241512995</v>
+        <v>387.3139397320879</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29329,28 +29408,28 @@
         <v>0.0983</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3109889805696539</v>
+        <v>-0.3109606655590925</v>
       </c>
       <c r="J10" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K10" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2678745523920009</v>
+        <v>0.2691249074525062</v>
       </c>
       <c r="M10" t="n">
-        <v>2.952304450665699</v>
+        <v>2.944114351884271</v>
       </c>
       <c r="N10" t="n">
-        <v>14.45346286569422</v>
+        <v>14.41264057183423</v>
       </c>
       <c r="O10" t="n">
-        <v>3.801771016999079</v>
+        <v>3.796398368432142</v>
       </c>
       <c r="P10" t="n">
-        <v>383.371467487197</v>
+        <v>383.3711718178516</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29407,28 +29486,28 @@
         <v>0.1068</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1992700393052083</v>
+        <v>-0.2010292820653833</v>
       </c>
       <c r="J11" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K11" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1562166239250128</v>
+        <v>0.1591277626786703</v>
       </c>
       <c r="M11" t="n">
-        <v>2.595407587735794</v>
+        <v>2.59673777479652</v>
       </c>
       <c r="N11" t="n">
-        <v>11.72777418806283</v>
+        <v>11.72049823909376</v>
       </c>
       <c r="O11" t="n">
-        <v>3.42458379778665</v>
+        <v>3.423521321547999</v>
       </c>
       <c r="P11" t="n">
-        <v>380.7536869822799</v>
+        <v>380.7720572440259</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29485,28 +29564,28 @@
         <v>0.1059</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2485345597505369</v>
+        <v>-0.250150007472288</v>
       </c>
       <c r="J12" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K12" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2269529556660665</v>
+        <v>0.23005703722616</v>
       </c>
       <c r="M12" t="n">
-        <v>2.572941177979166</v>
+        <v>2.571718199635297</v>
       </c>
       <c r="N12" t="n">
-        <v>11.50459995538148</v>
+        <v>11.49390082017351</v>
       </c>
       <c r="O12" t="n">
-        <v>3.391843150173881</v>
+        <v>3.390265597290795</v>
       </c>
       <c r="P12" t="n">
-        <v>386.3421158806062</v>
+        <v>386.3589846142211</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29563,28 +29642,28 @@
         <v>0.1001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2296326977145461</v>
+        <v>-0.2321687404526823</v>
       </c>
       <c r="J13" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K13" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1858967113520007</v>
+        <v>0.189595854905199</v>
       </c>
       <c r="M13" t="n">
-        <v>2.782548702389583</v>
+        <v>2.788662922822137</v>
       </c>
       <c r="N13" t="n">
-        <v>12.62708556659286</v>
+        <v>12.64514109369679</v>
       </c>
       <c r="O13" t="n">
-        <v>3.553461068675561</v>
+        <v>3.556000716211512</v>
       </c>
       <c r="P13" t="n">
-        <v>382.1604496937606</v>
+        <v>382.1869314107544</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29641,28 +29720,28 @@
         <v>0.1168</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2006378458289397</v>
+        <v>-0.2008357818571068</v>
       </c>
       <c r="J14" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K14" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1790275963417557</v>
+        <v>0.1802785769413138</v>
       </c>
       <c r="M14" t="n">
-        <v>2.432565898398482</v>
+        <v>2.426557950601198</v>
       </c>
       <c r="N14" t="n">
-        <v>10.09397340409754</v>
+        <v>10.06578663163923</v>
       </c>
       <c r="O14" t="n">
-        <v>3.17710141545679</v>
+        <v>3.172662388537304</v>
       </c>
       <c r="P14" t="n">
-        <v>386.8165430526423</v>
+        <v>386.8186099286464</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29719,28 +29798,28 @@
         <v>0.1167</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.06565701818304417</v>
+        <v>-0.06773464277944403</v>
       </c>
       <c r="J15" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K15" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01828602204248064</v>
+        <v>0.01950931377795928</v>
       </c>
       <c r="M15" t="n">
-        <v>2.780603338144697</v>
+        <v>2.78290145877466</v>
       </c>
       <c r="N15" t="n">
-        <v>12.65481823793455</v>
+        <v>12.65512799064854</v>
       </c>
       <c r="O15" t="n">
-        <v>3.557361134033843</v>
+        <v>3.557404670633991</v>
       </c>
       <c r="P15" t="n">
-        <v>384.1579135537466</v>
+        <v>384.1796084036614</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29797,28 +29876,28 @@
         <v>0.1572</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.05599475363429413</v>
+        <v>-0.05826658374315563</v>
       </c>
       <c r="J16" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K16" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01565079161689908</v>
+        <v>0.01696702870352951</v>
       </c>
       <c r="M16" t="n">
-        <v>2.580407554898251</v>
+        <v>2.585143694866932</v>
       </c>
       <c r="N16" t="n">
-        <v>10.78289631086736</v>
+        <v>10.79555003039063</v>
       </c>
       <c r="O16" t="n">
-        <v>3.283732070505656</v>
+        <v>3.285658233960226</v>
       </c>
       <c r="P16" t="n">
-        <v>383.2252361484145</v>
+        <v>383.2489589197606</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29875,28 +29954,28 @@
         <v>0.166</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.04538532634914384</v>
+        <v>-0.04822470815793804</v>
       </c>
       <c r="J17" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K17" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L17" t="n">
-        <v>0.009451791201583348</v>
+        <v>0.01066732220117073</v>
       </c>
       <c r="M17" t="n">
-        <v>2.691087101157273</v>
+        <v>2.697476708179948</v>
       </c>
       <c r="N17" t="n">
-        <v>11.80375776799875</v>
+        <v>11.83776000211211</v>
       </c>
       <c r="O17" t="n">
-        <v>3.435659728203413</v>
+        <v>3.440604598339093</v>
       </c>
       <c r="P17" t="n">
-        <v>389.1289280560629</v>
+        <v>389.1585772825398</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -29953,28 +30032,28 @@
         <v>0.1097</v>
       </c>
       <c r="I18" t="n">
-        <v>0.02124283891888901</v>
+        <v>0.02112774019389257</v>
       </c>
       <c r="J18" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K18" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L18" t="n">
-        <v>0.002306751269838481</v>
+        <v>0.002296812942521154</v>
       </c>
       <c r="M18" t="n">
-        <v>2.589650630392213</v>
+        <v>2.582918095938119</v>
       </c>
       <c r="N18" t="n">
-        <v>10.67208418052215</v>
+        <v>10.64204771408247</v>
       </c>
       <c r="O18" t="n">
-        <v>3.266815602467049</v>
+        <v>3.262215154474406</v>
       </c>
       <c r="P18" t="n">
-        <v>385.6244751679875</v>
+        <v>385.6256770451546</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30031,28 +30110,28 @@
         <v>0.1529</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.02162056300313392</v>
+        <v>-0.02524729745417872</v>
       </c>
       <c r="J19" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K19" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L19" t="n">
-        <v>0.001919850291460912</v>
+        <v>0.002611678490660685</v>
       </c>
       <c r="M19" t="n">
-        <v>2.826246466093889</v>
+        <v>2.837359897340322</v>
       </c>
       <c r="N19" t="n">
-        <v>13.28800911182682</v>
+        <v>13.36034686195975</v>
       </c>
       <c r="O19" t="n">
-        <v>3.645272158814321</v>
+        <v>3.655180824796463</v>
       </c>
       <c r="P19" t="n">
-        <v>378.9328597298655</v>
+        <v>378.9707306040034</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30109,28 +30188,28 @@
         <v>0.0994</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1227679553580488</v>
+        <v>-0.1248900971470573</v>
       </c>
       <c r="J20" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K20" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05382414931147583</v>
+        <v>0.05580432883824216</v>
       </c>
       <c r="M20" t="n">
-        <v>2.958900293679858</v>
+        <v>2.963188663813496</v>
       </c>
       <c r="N20" t="n">
-        <v>14.48747154602612</v>
+        <v>14.48416608637397</v>
       </c>
       <c r="O20" t="n">
-        <v>3.806241130830537</v>
+        <v>3.805806890315636</v>
       </c>
       <c r="P20" t="n">
-        <v>369.8331556361625</v>
+        <v>369.8553153408995</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30168,7 +30247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U354"/>
+  <dimension ref="A1:U355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68045,6 +68124,113 @@
         </is>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:10+00:00</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>-35.43349016422165,174.43064181619442</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>-35.4340489801884,174.43015053941377</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>-35.434697860758774,174.42979704575126</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>-35.4353627900354,174.42942392511782</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>-35.43606415755217,174.42924096354395</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>-35.436718244721156,174.42880770743628</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>-35.437399799005476,174.42847846657799</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>-35.438064028987895,174.4281357029724</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>-35.438730363971935,174.42780048306687</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>-35.439412610826125,174.4275022565244</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>-35.44008503861839,174.42725850511192</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>-35.440783677848394,174.42704132064225</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>-35.44148636869126,174.42688664139754</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>-35.4421874154659,174.42672318680968</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>-35.442895946191285,174.42661537295197</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>-35.44360083794045,174.4266009259277</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
+        <is>
+          <t>-35.44427457418999,174.42674587298072</t>
+        </is>
+      </c>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>-35.44496015224199,174.42693495478161</t>
+        </is>
+      </c>
+      <c r="T355" t="inlineStr">
+        <is>
+          <t>-35.445542081148275,174.42741489133542</t>
+        </is>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0075/nzd0075.xlsx
+++ b/data/nzd0075/nzd0075.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U355"/>
+  <dimension ref="A1:U357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24959,6 +24959,144 @@
       <c r="U355" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>370.97</v>
+      </c>
+      <c r="C356" t="n">
+        <v>376.68</v>
+      </c>
+      <c r="D356" t="n">
+        <v>369.56</v>
+      </c>
+      <c r="E356" t="n">
+        <v>369.73</v>
+      </c>
+      <c r="F356" t="n">
+        <v>382.83</v>
+      </c>
+      <c r="G356" t="n">
+        <v>367.3</v>
+      </c>
+      <c r="H356" t="n">
+        <v>374.95</v>
+      </c>
+      <c r="I356" t="n">
+        <v>375.74</v>
+      </c>
+      <c r="J356" t="n">
+        <v>372.39</v>
+      </c>
+      <c r="K356" t="n">
+        <v>369.08</v>
+      </c>
+      <c r="L356" t="n">
+        <v>376.55</v>
+      </c>
+      <c r="M356" t="n">
+        <v>369.89</v>
+      </c>
+      <c r="N356" t="n">
+        <v>379.15</v>
+      </c>
+      <c r="O356" t="n">
+        <v>375.68</v>
+      </c>
+      <c r="P356" t="n">
+        <v>374.62</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>379.62</v>
+      </c>
+      <c r="R356" t="n">
+        <v>382.83</v>
+      </c>
+      <c r="S356" t="n">
+        <v>369.21</v>
+      </c>
+      <c r="T356" t="n">
+        <v>360.72</v>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>370.43</v>
+      </c>
+      <c r="C357" t="n">
+        <v>376.13</v>
+      </c>
+      <c r="D357" t="n">
+        <v>368.93</v>
+      </c>
+      <c r="E357" t="n">
+        <v>369.91</v>
+      </c>
+      <c r="F357" t="n">
+        <v>384.54</v>
+      </c>
+      <c r="G357" t="n">
+        <v>367.67</v>
+      </c>
+      <c r="H357" t="n">
+        <v>376.64</v>
+      </c>
+      <c r="I357" t="n">
+        <v>376.62</v>
+      </c>
+      <c r="J357" t="n">
+        <v>373.19</v>
+      </c>
+      <c r="K357" t="n">
+        <v>368.26</v>
+      </c>
+      <c r="L357" t="n">
+        <v>376.44</v>
+      </c>
+      <c r="M357" t="n">
+        <v>369.51</v>
+      </c>
+      <c r="N357" t="n">
+        <v>379.06</v>
+      </c>
+      <c r="O357" t="n">
+        <v>376.68</v>
+      </c>
+      <c r="P357" t="n">
+        <v>374.62</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>379.62</v>
+      </c>
+      <c r="R357" t="n">
+        <v>382.83</v>
+      </c>
+      <c r="S357" t="n">
+        <v>369.21</v>
+      </c>
+      <c r="T357" t="n">
+        <v>360.72</v>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -24973,7 +25111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B364"/>
+  <dimension ref="A1:B366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28616,6 +28754,26 @@
       </c>
       <c r="B364" t="n">
         <v>0.97</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>-0.09</v>
       </c>
     </row>
   </sheetData>
@@ -28784,28 +28942,28 @@
         <v>0.0867</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02858531534495889</v>
+        <v>0.02329075506153412</v>
       </c>
       <c r="J2" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K2" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002209610764478454</v>
+        <v>0.001478843555005271</v>
       </c>
       <c r="M2" t="n">
-        <v>3.442831403776634</v>
+        <v>3.448638844070614</v>
       </c>
       <c r="N2" t="n">
-        <v>20.2512991083285</v>
+        <v>20.25470406790637</v>
       </c>
       <c r="O2" t="n">
-        <v>4.500144343054843</v>
+        <v>4.500522643861085</v>
       </c>
       <c r="P2" t="n">
-        <v>374.536738992472</v>
+        <v>374.5923500580205</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28862,28 +29020,28 @@
         <v>0.1675</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1134469495672261</v>
+        <v>0.1059114137663286</v>
       </c>
       <c r="J3" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K3" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04641547196207008</v>
+        <v>0.04058093597344981</v>
       </c>
       <c r="M3" t="n">
-        <v>2.899802517220041</v>
+        <v>2.925843231774207</v>
       </c>
       <c r="N3" t="n">
-        <v>14.37668725720784</v>
+        <v>14.52940711919983</v>
       </c>
       <c r="O3" t="n">
-        <v>3.791660224388235</v>
+        <v>3.811745941061633</v>
       </c>
       <c r="P3" t="n">
-        <v>379.8735679420296</v>
+        <v>379.9532442845397</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28940,28 +29098,28 @@
         <v>0.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03860404507572667</v>
+        <v>-0.04176709953898713</v>
       </c>
       <c r="J4" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K4" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0068770371550122</v>
+        <v>0.008117634233580251</v>
       </c>
       <c r="M4" t="n">
-        <v>2.638375249869819</v>
+        <v>2.639475435137543</v>
       </c>
       <c r="N4" t="n">
-        <v>11.81165231117896</v>
+        <v>11.78753656411824</v>
       </c>
       <c r="O4" t="n">
-        <v>3.436808448426965</v>
+        <v>3.43329820495078</v>
       </c>
       <c r="P4" t="n">
-        <v>373.0248472189903</v>
+        <v>373.0580710101622</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29018,28 +29176,28 @@
         <v>0.0907</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01641077396547192</v>
+        <v>-0.02384685370932766</v>
       </c>
       <c r="J5" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K5" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001312507561195386</v>
+        <v>0.002747590397611188</v>
       </c>
       <c r="M5" t="n">
-        <v>2.478839000415126</v>
+        <v>2.499745996389212</v>
       </c>
       <c r="N5" t="n">
-        <v>11.24680843104743</v>
+        <v>11.41402993895102</v>
       </c>
       <c r="O5" t="n">
-        <v>3.353626161492577</v>
+        <v>3.378465619027522</v>
       </c>
       <c r="P5" t="n">
-        <v>376.7241625825368</v>
+        <v>376.802264406326</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29096,28 +29254,28 @@
         <v>0.0612</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1267495863725924</v>
+        <v>-0.134594704796211</v>
       </c>
       <c r="J6" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K6" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L6" t="n">
-        <v>0.04737091637508306</v>
+        <v>0.05302089966880952</v>
       </c>
       <c r="M6" t="n">
-        <v>3.074591261684323</v>
+        <v>3.091262590157924</v>
       </c>
       <c r="N6" t="n">
-        <v>17.7316244793363</v>
+        <v>17.89258043207833</v>
       </c>
       <c r="O6" t="n">
-        <v>4.210893548801288</v>
+        <v>4.229962225845323</v>
       </c>
       <c r="P6" t="n">
-        <v>393.8863335689497</v>
+        <v>393.9687274290396</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29174,28 +29332,28 @@
         <v>0.0789</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.241148013683711</v>
+        <v>-0.242841221636359</v>
       </c>
       <c r="J7" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K7" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1442274013395602</v>
+        <v>0.1475337172714156</v>
       </c>
       <c r="M7" t="n">
-        <v>3.228663264720352</v>
+        <v>3.218802202644363</v>
       </c>
       <c r="N7" t="n">
-        <v>18.937443472616</v>
+        <v>18.84319191377846</v>
       </c>
       <c r="O7" t="n">
-        <v>4.351717301550734</v>
+        <v>4.340874556328305</v>
       </c>
       <c r="P7" t="n">
-        <v>375.3975311459216</v>
+        <v>375.4153141698399</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29252,28 +29410,28 @@
         <v>0.0707</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3514254437809355</v>
+        <v>-0.3543676891032523</v>
       </c>
       <c r="J8" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K8" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3086899051765881</v>
+        <v>0.3145257384057216</v>
       </c>
       <c r="M8" t="n">
-        <v>3.027873484994201</v>
+        <v>3.023495176879858</v>
       </c>
       <c r="N8" t="n">
-        <v>15.17959724396666</v>
+        <v>15.13445975027972</v>
       </c>
       <c r="O8" t="n">
-        <v>3.896100261025973</v>
+        <v>3.890303297980727</v>
       </c>
       <c r="P8" t="n">
-        <v>387.7428103152273</v>
+        <v>387.7737085641166</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29330,28 +29488,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3277680967500178</v>
+        <v>-0.3305039408382532</v>
       </c>
       <c r="J9" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K9" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2819708213300335</v>
+        <v>0.287602355227348</v>
       </c>
       <c r="M9" t="n">
-        <v>3.031960505156131</v>
+        <v>3.028150449705267</v>
       </c>
       <c r="N9" t="n">
-        <v>15.01463073857322</v>
+        <v>14.96259942357701</v>
       </c>
       <c r="O9" t="n">
-        <v>3.874871706079211</v>
+        <v>3.868151939050095</v>
       </c>
       <c r="P9" t="n">
-        <v>387.3139397320879</v>
+        <v>387.3426722974473</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29408,28 +29566,28 @@
         <v>0.0983</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3109606655590925</v>
+        <v>-0.313580942588908</v>
       </c>
       <c r="J10" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K10" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2691249074525062</v>
+        <v>0.2746501167966661</v>
       </c>
       <c r="M10" t="n">
-        <v>2.944114351884271</v>
+        <v>2.939121163220432</v>
       </c>
       <c r="N10" t="n">
-        <v>14.41264057183423</v>
+        <v>14.36120255931964</v>
       </c>
       <c r="O10" t="n">
-        <v>3.796398368432142</v>
+        <v>3.789617732610988</v>
       </c>
       <c r="P10" t="n">
-        <v>383.3711718178516</v>
+        <v>383.3986908006942</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29486,28 +29644,28 @@
         <v>0.1068</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2010292820653833</v>
+        <v>-0.2087743964358143</v>
       </c>
       <c r="J11" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K11" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1591277626786703</v>
+        <v>0.1683690354137197</v>
       </c>
       <c r="M11" t="n">
-        <v>2.59673777479652</v>
+        <v>2.620353369675013</v>
       </c>
       <c r="N11" t="n">
-        <v>11.72049823909376</v>
+        <v>11.90547230408195</v>
       </c>
       <c r="O11" t="n">
-        <v>3.423521321547999</v>
+        <v>3.450430741817889</v>
       </c>
       <c r="P11" t="n">
-        <v>380.7720572440259</v>
+        <v>380.8534076316477</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29564,28 +29722,28 @@
         <v>0.1059</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.250150007472288</v>
+        <v>-0.2538143134782367</v>
       </c>
       <c r="J12" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K12" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L12" t="n">
-        <v>0.23005703722616</v>
+        <v>0.2367463762465021</v>
       </c>
       <c r="M12" t="n">
-        <v>2.571718199635297</v>
+        <v>2.570885446736716</v>
       </c>
       <c r="N12" t="n">
-        <v>11.49390082017351</v>
+        <v>11.48527722289326</v>
       </c>
       <c r="O12" t="n">
-        <v>3.390265597290795</v>
+        <v>3.388993541288219</v>
       </c>
       <c r="P12" t="n">
-        <v>386.3589846142211</v>
+        <v>386.3974716730202</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29642,28 +29800,28 @@
         <v>0.1001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2321687404526823</v>
+        <v>-0.2394022016765703</v>
       </c>
       <c r="J13" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K13" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L13" t="n">
-        <v>0.189595854905199</v>
+        <v>0.198564473765506</v>
       </c>
       <c r="M13" t="n">
-        <v>2.788662922822137</v>
+        <v>2.812961193870871</v>
       </c>
       <c r="N13" t="n">
-        <v>12.64514109369679</v>
+        <v>12.79225326278197</v>
       </c>
       <c r="O13" t="n">
-        <v>3.556000716211512</v>
+        <v>3.576625960704022</v>
       </c>
       <c r="P13" t="n">
-        <v>382.1869314107544</v>
+        <v>382.2629065971118</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29720,28 +29878,28 @@
         <v>0.1168</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2008357818571068</v>
+        <v>-0.203540639995232</v>
       </c>
       <c r="J14" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K14" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1802785769413138</v>
+        <v>0.1857963776814687</v>
       </c>
       <c r="M14" t="n">
-        <v>2.426557950601198</v>
+        <v>2.424579063642256</v>
       </c>
       <c r="N14" t="n">
-        <v>10.06578663163923</v>
+        <v>10.03972430260139</v>
       </c>
       <c r="O14" t="n">
-        <v>3.172662388537304</v>
+        <v>3.168552398588572</v>
       </c>
       <c r="P14" t="n">
-        <v>386.8186099286464</v>
+        <v>386.847019699952</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29798,28 +29956,28 @@
         <v>0.1167</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.06773464277944403</v>
+        <v>-0.07485225122417694</v>
       </c>
       <c r="J15" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K15" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01950931377795928</v>
+        <v>0.0236402304525366</v>
       </c>
       <c r="M15" t="n">
-        <v>2.78290145877466</v>
+        <v>2.801826001384665</v>
       </c>
       <c r="N15" t="n">
-        <v>12.65512799064854</v>
+        <v>12.79651268005359</v>
       </c>
       <c r="O15" t="n">
-        <v>3.557404670633991</v>
+        <v>3.577221363020968</v>
       </c>
       <c r="P15" t="n">
-        <v>384.1796084036614</v>
+        <v>384.2543630481646</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -29876,28 +30034,28 @@
         <v>0.1572</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.05826658374315563</v>
+        <v>-0.06640294436158628</v>
       </c>
       <c r="J16" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K16" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01696702870352951</v>
+        <v>0.02166563388009346</v>
       </c>
       <c r="M16" t="n">
-        <v>2.585143694866932</v>
+        <v>2.613234058948763</v>
       </c>
       <c r="N16" t="n">
-        <v>10.79555003039063</v>
+        <v>11.01068430729954</v>
       </c>
       <c r="O16" t="n">
-        <v>3.285658233960226</v>
+        <v>3.318235119351783</v>
       </c>
       <c r="P16" t="n">
-        <v>383.2489589197606</v>
+        <v>383.3344163890973</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -29954,28 +30112,28 @@
         <v>0.166</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.04822470815793804</v>
+        <v>-0.05772181099570797</v>
       </c>
       <c r="J17" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K17" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01066732220117073</v>
+        <v>0.01494158433364934</v>
       </c>
       <c r="M17" t="n">
-        <v>2.697476708179948</v>
+        <v>2.730265644749587</v>
       </c>
       <c r="N17" t="n">
-        <v>11.83776000211211</v>
+        <v>12.14699800245721</v>
       </c>
       <c r="O17" t="n">
-        <v>3.440604598339093</v>
+        <v>3.485254366966235</v>
       </c>
       <c r="P17" t="n">
-        <v>389.1585772825398</v>
+        <v>389.25832684161</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30032,28 +30190,28 @@
         <v>0.1097</v>
       </c>
       <c r="I18" t="n">
-        <v>0.02112774019389257</v>
+        <v>0.01726238244916811</v>
       </c>
       <c r="J18" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K18" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L18" t="n">
-        <v>0.002296812942521154</v>
+        <v>0.001545709860459654</v>
       </c>
       <c r="M18" t="n">
-        <v>2.582918095938119</v>
+        <v>2.587633122026092</v>
       </c>
       <c r="N18" t="n">
-        <v>10.64204771408247</v>
+        <v>10.64450343233528</v>
       </c>
       <c r="O18" t="n">
-        <v>3.262215154474406</v>
+        <v>3.262591520913288</v>
       </c>
       <c r="P18" t="n">
-        <v>385.6256770451546</v>
+        <v>385.66627550558</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30110,28 +30268,28 @@
         <v>0.1529</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.02524729745417872</v>
+        <v>-0.0357002581485069</v>
       </c>
       <c r="J19" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K19" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L19" t="n">
-        <v>0.002611678490660685</v>
+        <v>0.005103202704932253</v>
       </c>
       <c r="M19" t="n">
-        <v>2.837359897340322</v>
+        <v>2.877900798593248</v>
       </c>
       <c r="N19" t="n">
-        <v>13.36034686195975</v>
+        <v>13.7404720943693</v>
       </c>
       <c r="O19" t="n">
-        <v>3.655180824796463</v>
+        <v>3.706814278375611</v>
       </c>
       <c r="P19" t="n">
-        <v>378.9707306040034</v>
+        <v>379.0805196895566</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30188,28 +30346,28 @@
         <v>0.0994</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1248900971470573</v>
+        <v>-0.1315617790251409</v>
       </c>
       <c r="J20" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="K20" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05580432883824216</v>
+        <v>0.06157179821426872</v>
       </c>
       <c r="M20" t="n">
-        <v>2.963188663813496</v>
+        <v>2.985912547361672</v>
       </c>
       <c r="N20" t="n">
-        <v>14.48416608637397</v>
+        <v>14.58822377073118</v>
       </c>
       <c r="O20" t="n">
-        <v>3.805806890315636</v>
+        <v>3.819453334016687</v>
       </c>
       <c r="P20" t="n">
-        <v>369.8553153408995</v>
+        <v>369.92538905554</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30247,7 +30405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U355"/>
+  <dimension ref="A1:U357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68231,6 +68389,220 @@
         </is>
       </c>
     </row>
+    <row r="356">
+      <c r="A356" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:40+00:00</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>-35.43347002038665,174.4306096095118</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>-35.434042489657244,174.43013529566196</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>-35.434694880171044,174.4297877071036</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>-35.43535629963984,174.42940527329367</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>-35.43605714571361,174.42921525630126</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>-35.43671642945296,174.42880218820912</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>-35.43738801838264,174.4284477443611</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>-35.43805714108456,174.42811368356303</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>-35.43872247397472,174.4277715331096</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>-35.43940325542612,174.42746728528707</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>-35.44008413767729,174.4272542385595</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>-35.440780010754,174.427022118202</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>-35.44148250965447,174.42686523288737</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>-35.4421838942251,174.42668886514653</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>-35.442893481847506,174.42658036077214</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>-35.44360200277375,174.42656349782393</t>
+        </is>
+      </c>
+      <c r="R356" t="inlineStr">
+        <is>
+          <t>-35.444282363382335,174.42671238801012</t>
+        </is>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>-35.444973940873346,174.4269080717623</t>
+        </is>
+      </c>
+      <c r="T356" t="inlineStr">
+        <is>
+          <t>-35.44555499157126,174.4273967845871</t>
+        </is>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:49+00:00</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>-35.43346706449706,174.43060488353257</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>-35.43404020132847,174.43012992126287</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>-35.4346928166868,174.4297812418864</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>-35.43535693456997,174.42940709792853</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>-35.436062019797106,174.4292331259695</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>-35.43671767324786,174.4288059699018</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>-35.43739448242668,174.42846460168033</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>-35.43805997349391,174.428122738273</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>-35.43872475267501,174.42777989410754</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>-35.439400958589815,174.42745869953535</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>-35.44008388991846,174.4272530652576</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>-35.44077923226428,174.4270180417065</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>-35.44148233512508,174.42686426466335</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>-35.44218501564044,174.4266997956122</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>-35.442893481847506,174.42658036077214</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>-35.44360200277375,174.42656349782393</t>
+        </is>
+      </c>
+      <c r="R357" t="inlineStr">
+        <is>
+          <t>-35.444282363382335,174.42671238801012</t>
+        </is>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>-35.444973940873346,174.4269080717623</t>
+        </is>
+      </c>
+      <c r="T357" t="inlineStr">
+        <is>
+          <t>-35.44555499157126,174.4273967845871</t>
+        </is>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0075/nzd0075.xlsx
+++ b/data/nzd0075/nzd0075.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U357"/>
+  <dimension ref="A1:U359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25095,6 +25095,144 @@
         <v>360.72</v>
       </c>
       <c r="U357" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>369.47</v>
+      </c>
+      <c r="C358" t="n">
+        <v>376.49</v>
+      </c>
+      <c r="D358" t="n">
+        <v>370.27</v>
+      </c>
+      <c r="E358" t="n">
+        <v>370.84</v>
+      </c>
+      <c r="F358" t="n">
+        <v>386.99</v>
+      </c>
+      <c r="G358" t="n">
+        <v>367.76</v>
+      </c>
+      <c r="H358" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="I358" t="n">
+        <v>377.47</v>
+      </c>
+      <c r="J358" t="n">
+        <v>374.95</v>
+      </c>
+      <c r="K358" t="n">
+        <v>368.56</v>
+      </c>
+      <c r="L358" t="n">
+        <v>376.27</v>
+      </c>
+      <c r="M358" t="n">
+        <v>370.81</v>
+      </c>
+      <c r="N358" t="n">
+        <v>378.74</v>
+      </c>
+      <c r="O358" t="n">
+        <v>378.02</v>
+      </c>
+      <c r="P358" t="n">
+        <v>376.81</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>382.55</v>
+      </c>
+      <c r="R358" t="n">
+        <v>382.85</v>
+      </c>
+      <c r="S358" t="n">
+        <v>372.64</v>
+      </c>
+      <c r="T358" t="n">
+        <v>362.11</v>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>369.86</v>
+      </c>
+      <c r="C359" t="n">
+        <v>375.84</v>
+      </c>
+      <c r="D359" t="n">
+        <v>369.71</v>
+      </c>
+      <c r="E359" t="n">
+        <v>370.72</v>
+      </c>
+      <c r="F359" t="n">
+        <v>386.32</v>
+      </c>
+      <c r="G359" t="n">
+        <v>368.17</v>
+      </c>
+      <c r="H359" t="n">
+        <v>378.1</v>
+      </c>
+      <c r="I359" t="n">
+        <v>377.63</v>
+      </c>
+      <c r="J359" t="n">
+        <v>376.78</v>
+      </c>
+      <c r="K359" t="n">
+        <v>369.37</v>
+      </c>
+      <c r="L359" t="n">
+        <v>377.83</v>
+      </c>
+      <c r="M359" t="n">
+        <v>372.09</v>
+      </c>
+      <c r="N359" t="n">
+        <v>380.26</v>
+      </c>
+      <c r="O359" t="n">
+        <v>378.27</v>
+      </c>
+      <c r="P359" t="n">
+        <v>377.48</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>382.56</v>
+      </c>
+      <c r="R359" t="n">
+        <v>384.59</v>
+      </c>
+      <c r="S359" t="n">
+        <v>374.56</v>
+      </c>
+      <c r="T359" t="n">
+        <v>364.16</v>
+      </c>
+      <c r="U359" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -25111,7 +25249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B366"/>
+  <dimension ref="A1:B368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28774,6 +28912,26 @@
       </c>
       <c r="B366" t="n">
         <v>-0.09</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
@@ -28942,28 +29100,28 @@
         <v>0.0867</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02329075506153412</v>
+        <v>0.01697321676001469</v>
       </c>
       <c r="J2" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K2" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001478843555005271</v>
+        <v>0.0007896323234821701</v>
       </c>
       <c r="M2" t="n">
-        <v>3.448638844070614</v>
+        <v>3.459344828708767</v>
       </c>
       <c r="N2" t="n">
-        <v>20.25470406790637</v>
+        <v>20.31080278780043</v>
       </c>
       <c r="O2" t="n">
-        <v>4.500522643861085</v>
+        <v>4.506750801608675</v>
       </c>
       <c r="P2" t="n">
-        <v>374.5923500580205</v>
+        <v>374.6589399632593</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -29020,28 +29178,28 @@
         <v>0.1675</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1059114137663286</v>
+        <v>0.09830955462861661</v>
       </c>
       <c r="J3" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K3" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04058093597344981</v>
+        <v>0.03504415657953597</v>
       </c>
       <c r="M3" t="n">
-        <v>2.925843231774207</v>
+        <v>2.952513148223403</v>
       </c>
       <c r="N3" t="n">
-        <v>14.52940711919983</v>
+        <v>14.68997412782144</v>
       </c>
       <c r="O3" t="n">
-        <v>3.811745941061633</v>
+        <v>3.83275020420343</v>
       </c>
       <c r="P3" t="n">
-        <v>379.9532442845397</v>
+        <v>380.033906673073</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29098,28 +29256,28 @@
         <v>0.1053</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04176709953898713</v>
+        <v>-0.04398525333529795</v>
       </c>
       <c r="J4" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K4" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008117634233580251</v>
+        <v>0.009095694998649373</v>
       </c>
       <c r="M4" t="n">
-        <v>2.639475435137543</v>
+        <v>2.635818998543548</v>
       </c>
       <c r="N4" t="n">
-        <v>11.78753656411824</v>
+        <v>11.74293838378798</v>
       </c>
       <c r="O4" t="n">
-        <v>3.43329820495078</v>
+        <v>3.426797102804305</v>
       </c>
       <c r="P4" t="n">
-        <v>373.0580710101622</v>
+        <v>373.0814532749575</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29176,28 +29334,28 @@
         <v>0.0907</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02384685370932766</v>
+        <v>-0.02996872041419514</v>
       </c>
       <c r="J5" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K5" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002747590397611188</v>
+        <v>0.004328938587719544</v>
       </c>
       <c r="M5" t="n">
-        <v>2.499745996389212</v>
+        <v>2.514972656265439</v>
       </c>
       <c r="N5" t="n">
-        <v>11.41402993895102</v>
+        <v>11.50900081401223</v>
       </c>
       <c r="O5" t="n">
-        <v>3.378465619027522</v>
+        <v>3.392491829616134</v>
       </c>
       <c r="P5" t="n">
-        <v>376.802264406326</v>
+        <v>376.866793183588</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29254,28 +29412,28 @@
         <v>0.0612</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.134594704796211</v>
+        <v>-0.1388126619185608</v>
       </c>
       <c r="J6" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K6" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05302089966880952</v>
+        <v>0.05667555218812226</v>
       </c>
       <c r="M6" t="n">
-        <v>3.091262590157924</v>
+        <v>3.092473092852106</v>
       </c>
       <c r="N6" t="n">
-        <v>17.89258043207833</v>
+        <v>17.86858882556213</v>
       </c>
       <c r="O6" t="n">
-        <v>4.229962225845323</v>
+        <v>4.22712536194068</v>
       </c>
       <c r="P6" t="n">
-        <v>393.9687274290396</v>
+        <v>394.0131892534086</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29332,28 +29490,28 @@
         <v>0.0789</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.242841221636359</v>
+        <v>-0.2439156046486695</v>
       </c>
       <c r="J7" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K7" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1475337172714156</v>
+        <v>0.1502741336200222</v>
       </c>
       <c r="M7" t="n">
-        <v>3.218802202644363</v>
+        <v>3.205999221082015</v>
       </c>
       <c r="N7" t="n">
-        <v>18.84319191377846</v>
+        <v>18.74306181030862</v>
       </c>
       <c r="O7" t="n">
-        <v>4.340874556328305</v>
+        <v>4.329325791657244</v>
       </c>
       <c r="P7" t="n">
-        <v>375.4153141698399</v>
+        <v>375.4266377281448</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29410,28 +29568,28 @@
         <v>0.0707</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3543676891032523</v>
+        <v>-0.3549149613187626</v>
       </c>
       <c r="J8" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K8" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3145257384057216</v>
+        <v>0.3179935570932829</v>
       </c>
       <c r="M8" t="n">
-        <v>3.023495176879858</v>
+        <v>3.008925849706067</v>
       </c>
       <c r="N8" t="n">
-        <v>15.13445975027972</v>
+        <v>15.05169923951061</v>
       </c>
       <c r="O8" t="n">
-        <v>3.890303297980727</v>
+        <v>3.879651948243632</v>
       </c>
       <c r="P8" t="n">
-        <v>387.7737085641166</v>
+        <v>387.7794755248104</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29488,28 +29646,28 @@
         <v>0.08740000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3305039408382532</v>
+        <v>-0.3315710953694365</v>
       </c>
       <c r="J9" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K9" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L9" t="n">
-        <v>0.287602355227348</v>
+        <v>0.2915501749103439</v>
       </c>
       <c r="M9" t="n">
-        <v>3.028150449705267</v>
+        <v>3.016329885538476</v>
       </c>
       <c r="N9" t="n">
-        <v>14.96259942357701</v>
+        <v>14.88387039552859</v>
       </c>
       <c r="O9" t="n">
-        <v>3.868151939050095</v>
+        <v>3.857961948429324</v>
       </c>
       <c r="P9" t="n">
-        <v>387.3426722974473</v>
+        <v>387.3539203605079</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -29566,28 +29724,28 @@
         <v>0.0983</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.313580942588908</v>
+        <v>-0.3125911798423866</v>
       </c>
       <c r="J10" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K10" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2746501167966661</v>
+        <v>0.2758725647864383</v>
       </c>
       <c r="M10" t="n">
-        <v>2.939121163220432</v>
+        <v>2.92826754139365</v>
       </c>
       <c r="N10" t="n">
-        <v>14.36120255931964</v>
+        <v>14.2898177330414</v>
       </c>
       <c r="O10" t="n">
-        <v>3.789617732610988</v>
+        <v>3.780187526173986</v>
       </c>
       <c r="P10" t="n">
-        <v>383.3986908006942</v>
+        <v>383.3882531101755</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -29644,28 +29802,28 @@
         <v>0.1068</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2087743964358143</v>
+        <v>-0.2159396899662207</v>
       </c>
       <c r="J11" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K11" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1683690354137197</v>
+        <v>0.1772705707650367</v>
       </c>
       <c r="M11" t="n">
-        <v>2.620353369675013</v>
+        <v>2.641954536794156</v>
       </c>
       <c r="N11" t="n">
-        <v>11.90547230408195</v>
+        <v>12.05735636196853</v>
       </c>
       <c r="O11" t="n">
-        <v>3.450430741817889</v>
+        <v>3.472370424071794</v>
       </c>
       <c r="P11" t="n">
-        <v>380.8534076316477</v>
+        <v>380.9289322807857</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -29722,28 +29880,28 @@
         <v>0.1059</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2538143134782367</v>
+        <v>-0.2567102669052071</v>
       </c>
       <c r="J12" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K12" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2367463762465021</v>
+        <v>0.2426421963601454</v>
       </c>
       <c r="M12" t="n">
-        <v>2.570885446736716</v>
+        <v>2.567176536165634</v>
       </c>
       <c r="N12" t="n">
-        <v>11.48527722289326</v>
+        <v>11.460089600979</v>
       </c>
       <c r="O12" t="n">
-        <v>3.388993541288219</v>
+        <v>3.385275409915566</v>
       </c>
       <c r="P12" t="n">
-        <v>386.3974716730202</v>
+        <v>386.4279926756267</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -29800,28 +29958,28 @@
         <v>0.1001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2394022016765703</v>
+        <v>-0.2444026478416352</v>
       </c>
       <c r="J13" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K13" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L13" t="n">
-        <v>0.198564473765506</v>
+        <v>0.2059765705815816</v>
       </c>
       <c r="M13" t="n">
-        <v>2.812961193870871</v>
+        <v>2.825049497335798</v>
       </c>
       <c r="N13" t="n">
-        <v>12.79225326278197</v>
+        <v>12.82903731465314</v>
       </c>
       <c r="O13" t="n">
-        <v>3.576625960704022</v>
+        <v>3.581764553213002</v>
       </c>
       <c r="P13" t="n">
-        <v>382.2629065971118</v>
+        <v>382.3156110734172</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -29878,28 +30036,28 @@
         <v>0.1168</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.203540639995232</v>
+        <v>-0.2056926728926743</v>
       </c>
       <c r="J14" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K14" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1857963776814687</v>
+        <v>0.1906570538602911</v>
       </c>
       <c r="M14" t="n">
-        <v>2.424579063642256</v>
+        <v>2.420310530919837</v>
       </c>
       <c r="N14" t="n">
-        <v>10.03972430260139</v>
+        <v>10.00654406316368</v>
       </c>
       <c r="O14" t="n">
-        <v>3.168552398588572</v>
+        <v>3.16331219818147</v>
       </c>
       <c r="P14" t="n">
-        <v>386.847019699952</v>
+        <v>386.8696993952793</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -29956,28 +30114,28 @@
         <v>0.1167</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.07485225122417694</v>
+        <v>-0.07952573558717224</v>
       </c>
       <c r="J15" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K15" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0236402304525366</v>
+        <v>0.02675451941256735</v>
       </c>
       <c r="M15" t="n">
-        <v>2.801826001384665</v>
+        <v>2.808972753692661</v>
       </c>
       <c r="N15" t="n">
-        <v>12.79651268005359</v>
+        <v>12.81761999152078</v>
       </c>
       <c r="O15" t="n">
-        <v>3.577221363020968</v>
+        <v>3.580170385822549</v>
       </c>
       <c r="P15" t="n">
-        <v>384.2543630481646</v>
+        <v>384.3036239266867</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -30034,28 +30192,28 @@
         <v>0.1572</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.06640294436158628</v>
+        <v>-0.07141903677999067</v>
       </c>
       <c r="J16" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K16" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02166563388009346</v>
+        <v>0.02505881191192405</v>
       </c>
       <c r="M16" t="n">
-        <v>2.613234058948763</v>
+        <v>2.625464541838572</v>
       </c>
       <c r="N16" t="n">
-        <v>11.01068430729954</v>
+        <v>11.05637294819078</v>
       </c>
       <c r="O16" t="n">
-        <v>3.318235119351783</v>
+        <v>3.325112471509916</v>
       </c>
       <c r="P16" t="n">
-        <v>383.3344163890973</v>
+        <v>383.3872874599968</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -30112,28 +30270,28 @@
         <v>0.166</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.05772181099570797</v>
+        <v>-0.06359199306856922</v>
       </c>
       <c r="J17" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K17" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01494158433364934</v>
+        <v>0.0180962664918799</v>
       </c>
       <c r="M17" t="n">
-        <v>2.730265644749587</v>
+        <v>2.746082897055256</v>
       </c>
       <c r="N17" t="n">
-        <v>12.14699800245721</v>
+        <v>12.22507583855249</v>
       </c>
       <c r="O17" t="n">
-        <v>3.485254366966235</v>
+        <v>3.496437592543657</v>
       </c>
       <c r="P17" t="n">
-        <v>389.25832684161</v>
+        <v>389.3202023320615</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -30190,28 +30348,28 @@
         <v>0.1097</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01726238244916811</v>
+        <v>0.01451840474062819</v>
       </c>
       <c r="J18" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K18" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L18" t="n">
-        <v>0.001545709860459654</v>
+        <v>0.001104463873738859</v>
       </c>
       <c r="M18" t="n">
-        <v>2.587633122026092</v>
+        <v>2.587316056582488</v>
       </c>
       <c r="N18" t="n">
-        <v>10.64450343233528</v>
+        <v>10.62118850340296</v>
       </c>
       <c r="O18" t="n">
-        <v>3.262591520913288</v>
+        <v>3.25901649326955</v>
       </c>
       <c r="P18" t="n">
-        <v>385.66627550558</v>
+        <v>385.695194116367</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -30268,28 +30426,28 @@
         <v>0.1529</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0357002581485069</v>
+        <v>-0.04084381866348961</v>
       </c>
       <c r="J19" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K19" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L19" t="n">
-        <v>0.005103202704932253</v>
+        <v>0.006699182487482136</v>
       </c>
       <c r="M19" t="n">
-        <v>2.877900798593248</v>
+        <v>2.890904870375164</v>
       </c>
       <c r="N19" t="n">
-        <v>13.7404720943693</v>
+        <v>13.78092673741873</v>
       </c>
       <c r="O19" t="n">
-        <v>3.706814278375611</v>
+        <v>3.712267061704846</v>
       </c>
       <c r="P19" t="n">
-        <v>379.0805196895566</v>
+        <v>379.1347309959049</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -30346,28 +30504,28 @@
         <v>0.0994</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1315617790251409</v>
+        <v>-0.1352760716071175</v>
       </c>
       <c r="J20" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K20" t="n">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L20" t="n">
-        <v>0.06157179821426872</v>
+        <v>0.06539488171496088</v>
       </c>
       <c r="M20" t="n">
-        <v>2.985912547361672</v>
+        <v>2.990955246183773</v>
       </c>
       <c r="N20" t="n">
-        <v>14.58822377073118</v>
+        <v>14.57112631034422</v>
       </c>
       <c r="O20" t="n">
-        <v>3.819453334016687</v>
+        <v>3.817214470048051</v>
       </c>
       <c r="P20" t="n">
-        <v>369.92538905554</v>
+        <v>369.9645345550921</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -30405,7 +30563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U357"/>
+  <dimension ref="A1:U359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68603,6 +68761,220 @@
         </is>
       </c>
     </row>
+    <row r="358">
+      <c r="A358" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:30+00:00</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>-35.43346180958174,174.4305964817925</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>-35.4340416991437,174.43013343905133</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>-35.434697205684614,174.4297949933012</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>-35.43536021504187,174.42941652520898</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>-35.436069003128395,174.4292587287141</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>-35.43671797579253,174.42880688977297</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>-35.43739777182096,174.42847317996214</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>-35.43806270934318,174.42813148430025</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>-35.43872976581355,174.4277982883046</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>-35.43940179889585,174.427461840664</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>-35.44008350701842,174.42725125197288</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>-35.440781895517986,174.42703198761242</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>-35.441481714576064,174.42686082208903</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>-35.44218651833544,174.42671444243666</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>-35.44289517367082,174.4266043973468</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>-35.44360099896222,174.42659575204283</t>
+        </is>
+      </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>-35.44428231408368,174.42671259994032</t>
+        </is>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>-35.44495751899576,174.42694008869051</t>
+        </is>
+      </c>
+      <c r="T358" t="inlineStr">
+        <is>
+          <t>-35.445546759696356,174.4274083297163</t>
+        </is>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>-35.433463944391164,174.43059989499926</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>-35.434038994755035,174.4301270874889</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>-35.43469537147677,174.4297892464411</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>-35.435359791755204,174.42941530878565</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>-35.43606709340161,174.4292517271468</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>-35.43671935405159,174.42881108029744</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>-35.437400066746804,174.42847916481028</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>-35.438063224326505,174.42813313061131</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>-35.438734978335255,174.42781741409135</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>-35.439404067721746,174.42747032171155</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>-35.440087020688296,174.42726789152755</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>-35.44078451779695,174.42704571896675</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>-35.44148466218301,174.42687717431744</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>-35.44218679868876,174.4267171750532</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>-35.44289569125965,174.42661175100227</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>-35.44360099553623,174.42659586212548</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>-35.444278025099116,174.426731037868</t>
+        </is>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>-35.44494832657088,174.42695801069704</t>
+        </is>
+      </c>
+      <c r="T359" t="inlineStr">
+        <is>
+          <t>-35.44553461915949,174.42742535670106</t>
+        </is>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
